--- a/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_BE_PIN.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_BE_PIN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nhatm\AppData\Local\Temp\claude\E--Out-Job-Chu-Giap-Web-t-nh-neo-b-\4941c4bc-fff6-410b-95cf-e91fd3b09d53\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A37C7F5-4940-444B-B49C-66B8758FCE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{53A0696A-3022-49E6-9A7B-8511568AF459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4110" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,7 +93,7 @@
     <t>BV</t>
   </si>
   <si>
-    <t>Tổng 18.240 tấm trên bản vẽ 22/10; Pre-FS và web: 16.892 tấm (xem DoiChieu_MatBang)</t>
+    <t>ĐÃ CHỐT 18.240 tấm (Chủ đầu tư 22/10/2026), theo bảng từng tờ; Pre-FS cũ ghi 16.892 tấm</t>
   </si>
   <si>
     <t>Inverter SG-510HX</t>
@@ -1632,7 +1632,7 @@
     <t>ĐỐI CHIẾU TỪNG TỜ CT-BP (22/10/2026) VỚI MẶT BẰNG BÈ MÀ WEB DÙNG TÍNH NEO (nhập từ tờ MB-B01-01)</t>
   </si>
   <si>
-    <t>Đường bao bè đo trên ảnh từng tờ CT-BP (tỷ lệ in trên tờ, gồm cả mép phao nên rộng hơn 1–2 m); mặt bằng trên web lấy đường bao bè của tờ MB-B01-01. Số tấm pin trên web lấy đúng bảng từng tờ (Pre-FS ghi 16.892 tấm, bản vẽ 22/10 có 18.240 tấm).</t>
+    <t>Đường bao bè đo trên ảnh từng tờ CT-BP (tỷ lệ in trên tờ, gồm cả mép phao nên rộng hơn 1–2 m); mặt bằng trên web lấy đường bao bè của tờ MB-B01-01. Số tấm pin trên web lấy đúng bảng từng tờ — ĐÃ CHỐT 18.240 tấm (Pre-FS cũ ghi 16.892).</t>
   </si>
   <si>
     <t>Tỷ lệ tờ</t>
@@ -1950,7 +1950,7 @@
     <t>Mặt bằng neo (số dây, vị trí bích) là của web, tính trên mặt bằng bè 22/10/2026 (đường bao lấy từ tờ MB-B01-01, đặt về tọa độ PA2: so với PA2 chỉ BÈ 4 và BÈ 6 đổi hình). Đường bao đo trên từng tờ CT-BP rộng hơn 1–2 m vì gồm cả mép phao (sheet DoiChieu_MatBang).</t>
   </si>
   <si>
-    <t>Tổng tấm pin trên bản vẽ 18.240 tấm (13,5 MWp với tấm 740 Wp), khác Pre-FS 16.892 tấm (12,5 MWp). Tờ BÈ 2 có 1 dải 28 tấm ghi chú "be 1"; BÈ 4 ghi 80,43 string (2.252 tấm không chia hết cho 28). Cần thiết kế điện xác nhận.</t>
+    <t>Số tấm pin ĐÃ CHỐT 18.240 tấm (Chủ đầu tư 22/10/2026; 13,5 MWp với tấm 740 Wp — Pre-FS cũ ghi 16.892 tấm, 12,5 MWp). Lực gió và lực dây trên web tính theo số tấm từng bè này. Còn để thiết kế điện xem: tờ BÈ 2 có 1 dải 28 tấm ghi chú "be 1"; BÈ 4 ghi 80,43 string (2.252 tấm không chia hết cho 28).</t>
   </si>
   <si>
     <t>Khối lượng thép theo tiết diện GIẢ ĐỊNH (C52 ≈ 2,36 kg/m; hộp 40×60×2,0 ≈ 3,01 kg/m) vì chưa có catalogue tiết diện của nhà sản xuất.</t>

--- a/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_BE_PIN.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_BE_PIN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nhatm\AppData\Local\Temp\claude\E--Out-Job-Chu-Giap-Web-t-nh-neo-b-\4941c4bc-fff6-410b-95cf-e91fd3b09d53\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nhatm\AppData\Local\Temp\claude\E--Out-Job-Chu-Giap-Web-t-nh-neo-b-\76591ad0-fd64-4fcb-9443-d8c50853fa07\scratchpad\boq\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53A0696A-3022-49E6-9A7B-8511568AF459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAD864AC-9C11-42E0-9F3C-E4D1BF436C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4110" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="E29" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 1",GiaCuong_UocTinh!$L$4:$L$375)</f>
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="F29" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 2",GiaCuong_UocTinh!$L$4:$L$375)</f>
@@ -4838,27 +4838,27 @@
       </c>
       <c r="I29" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 5",GiaCuong_UocTinh!$L$4:$L$375)</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J29" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 6",GiaCuong_UocTinh!$L$4:$L$375)</f>
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K29" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 7",GiaCuong_UocTinh!$L$4:$L$375)</f>
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="L29" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 8",GiaCuong_UocTinh!$L$4:$L$375)</f>
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="M29" s="8">
         <f t="shared" ref="M29:M36" si="6">SUM(E29:L29)</f>
-        <v>532</v>
+        <v>668</v>
       </c>
       <c r="N29" s="8">
         <f>M29</f>
-        <v>532</v>
+        <v>668</v>
       </c>
       <c r="O29" s="7" t="s">
         <v>38</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="E30" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 1",GiaCuong_UocTinh!$M$4:$M$375)</f>
-        <v>1050</v>
+        <v>1770</v>
       </c>
       <c r="F30" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 2",GiaCuong_UocTinh!$M$4:$M$375)</f>
@@ -4896,27 +4896,27 @@
       </c>
       <c r="I30" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 5",GiaCuong_UocTinh!$M$4:$M$375)</f>
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="J30" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 6",GiaCuong_UocTinh!$M$4:$M$375)</f>
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="K30" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 7",GiaCuong_UocTinh!$M$4:$M$375)</f>
-        <v>1200</v>
+        <v>1845</v>
       </c>
       <c r="L30" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 8",GiaCuong_UocTinh!$M$4:$M$375)</f>
-        <v>990</v>
+        <v>1710</v>
       </c>
       <c r="M30" s="8">
         <f t="shared" si="6"/>
-        <v>7980</v>
+        <v>10020</v>
       </c>
       <c r="N30" s="8">
         <f>M30</f>
-        <v>7980</v>
+        <v>10020</v>
       </c>
       <c r="O30" s="7" t="s">
         <v>38</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="E31" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 1",GiaCuong_UocTinh!$N$4:$N$375)</f>
-        <v>210</v>
+        <v>354</v>
       </c>
       <c r="F31" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 2",GiaCuong_UocTinh!$N$4:$N$375)</f>
@@ -4952,27 +4952,27 @@
       </c>
       <c r="I31" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 5",GiaCuong_UocTinh!$N$4:$N$375)</f>
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J31" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 6",GiaCuong_UocTinh!$N$4:$N$375)</f>
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K31" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 7",GiaCuong_UocTinh!$N$4:$N$375)</f>
-        <v>240</v>
+        <v>369</v>
       </c>
       <c r="L31" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 8",GiaCuong_UocTinh!$N$4:$N$375)</f>
-        <v>198</v>
+        <v>342</v>
       </c>
       <c r="M31" s="8">
         <f t="shared" si="6"/>
-        <v>1596</v>
+        <v>2004</v>
       </c>
       <c r="N31" s="8">
         <f>M31</f>
-        <v>1596</v>
+        <v>2004</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>38</v>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="E32" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 1",GiaCuong_UocTinh!$O$4:$O$375)</f>
-        <v>140</v>
+        <v>236</v>
       </c>
       <c r="F32" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 2",GiaCuong_UocTinh!$O$4:$O$375)</f>
@@ -5008,27 +5008,27 @@
       </c>
       <c r="I32" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 5",GiaCuong_UocTinh!$O$4:$O$375)</f>
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J32" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 6",GiaCuong_UocTinh!$O$4:$O$375)</f>
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K32" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 7",GiaCuong_UocTinh!$O$4:$O$375)</f>
-        <v>160</v>
+        <v>246</v>
       </c>
       <c r="L32" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 8",GiaCuong_UocTinh!$O$4:$O$375)</f>
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="M32" s="8">
         <f t="shared" si="6"/>
-        <v>1064</v>
+        <v>1336</v>
       </c>
       <c r="N32" s="8">
         <f>ROUNDUP(M32*(1+GiaDinh!$C$14/100),0)</f>
-        <v>1096</v>
+        <v>1377</v>
       </c>
       <c r="O32" s="7" t="s">
         <v>38</v>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="E33" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 1",GiaCuong_UocTinh!$P$4:$P$375)</f>
-        <v>910</v>
+        <v>1534</v>
       </c>
       <c r="F33" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 2",GiaCuong_UocTinh!$P$4:$P$375)</f>
@@ -5064,27 +5064,27 @@
       </c>
       <c r="I33" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 5",GiaCuong_UocTinh!$P$4:$P$375)</f>
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="J33" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 6",GiaCuong_UocTinh!$P$4:$P$375)</f>
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="K33" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 7",GiaCuong_UocTinh!$P$4:$P$375)</f>
-        <v>1040</v>
+        <v>1599</v>
       </c>
       <c r="L33" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 8",GiaCuong_UocTinh!$P$4:$P$375)</f>
-        <v>858</v>
+        <v>1482</v>
       </c>
       <c r="M33" s="8">
         <f t="shared" si="6"/>
-        <v>6916</v>
+        <v>8684</v>
       </c>
       <c r="N33" s="8">
         <f>ROUNDUP(M33*(1+GiaDinh!$C$14/100),0)</f>
-        <v>7124</v>
+        <v>8945</v>
       </c>
       <c r="O33" s="7" t="s">
         <v>38</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E34" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 1",GiaCuong_UocTinh!$Q$4:$Q$375)</f>
-        <v>1820</v>
+        <v>3068</v>
       </c>
       <c r="F34" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 2",GiaCuong_UocTinh!$Q$4:$Q$375)</f>
@@ -5122,27 +5122,27 @@
       </c>
       <c r="I34" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 5",GiaCuong_UocTinh!$Q$4:$Q$375)</f>
-        <v>1014</v>
+        <v>988</v>
       </c>
       <c r="J34" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 6",GiaCuong_UocTinh!$Q$4:$Q$375)</f>
-        <v>1248</v>
+        <v>1196</v>
       </c>
       <c r="K34" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 7",GiaCuong_UocTinh!$Q$4:$Q$375)</f>
-        <v>2080</v>
+        <v>3198</v>
       </c>
       <c r="L34" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 8",GiaCuong_UocTinh!$Q$4:$Q$375)</f>
-        <v>1716</v>
+        <v>2964</v>
       </c>
       <c r="M34" s="8">
         <f t="shared" si="6"/>
-        <v>13832</v>
+        <v>17368</v>
       </c>
       <c r="N34" s="8">
         <f>ROUNDUP(M34*(1+GiaDinh!$C$14/100),0)</f>
-        <v>14247</v>
+        <v>17890</v>
       </c>
       <c r="O34" s="7" t="s">
         <v>38</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="E35" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 1",GiaCuong_UocTinh!$R$4:$R$375)</f>
-        <v>910</v>
+        <v>1534</v>
       </c>
       <c r="F35" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 2",GiaCuong_UocTinh!$R$4:$R$375)</f>
@@ -5180,27 +5180,27 @@
       </c>
       <c r="I35" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 5",GiaCuong_UocTinh!$R$4:$R$375)</f>
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="J35" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 6",GiaCuong_UocTinh!$R$4:$R$375)</f>
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="K35" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 7",GiaCuong_UocTinh!$R$4:$R$375)</f>
-        <v>1040</v>
+        <v>1599</v>
       </c>
       <c r="L35" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 8",GiaCuong_UocTinh!$R$4:$R$375)</f>
-        <v>858</v>
+        <v>1482</v>
       </c>
       <c r="M35" s="8">
         <f t="shared" si="6"/>
-        <v>6916</v>
+        <v>8684</v>
       </c>
       <c r="N35" s="8">
         <f>ROUNDUP(M35*(1+GiaDinh!$C$14/100),0)</f>
-        <v>7124</v>
+        <v>8945</v>
       </c>
       <c r="O35" s="7" t="s">
         <v>38</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="E36" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 1",GiaCuong_UocTinh!$S$4:$S$375)</f>
-        <v>3160.5000000000018</v>
+        <v>5327.7000000000044</v>
       </c>
       <c r="F36" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 2",GiaCuong_UocTinh!$S$4:$S$375)</f>
@@ -5238,27 +5238,27 @@
       </c>
       <c r="I36" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 5",GiaCuong_UocTinh!$S$4:$S$375)</f>
-        <v>1760.8500000000013</v>
+        <v>1715.7000000000012</v>
       </c>
       <c r="J36" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 6",GiaCuong_UocTinh!$S$4:$S$375)</f>
-        <v>2167.2000000000021</v>
+        <v>2076.9000000000019</v>
       </c>
       <c r="K36" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 7",GiaCuong_UocTinh!$S$4:$S$375)</f>
-        <v>3612.0000000000018</v>
+        <v>5553.4500000000025</v>
       </c>
       <c r="L36" s="8">
         <f>SUMIF(GiaCuong_UocTinh!$A$4:$A$375,"BÈ 8",GiaCuong_UocTinh!$S$4:$S$375)</f>
-        <v>2979.9000000000019</v>
+        <v>5147.1000000000049</v>
       </c>
       <c r="M36" s="8">
         <f t="shared" si="6"/>
-        <v>24019.800000000017</v>
+        <v>30160.200000000026</v>
       </c>
       <c r="N36" s="8">
         <f>M36</f>
-        <v>24019.800000000017</v>
+        <v>30160.200000000026</v>
       </c>
       <c r="O36" s="7" t="s">
         <v>38</v>
@@ -6501,11 +6501,11 @@
         <v>4</v>
       </c>
       <c r="F4" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G4" s="12">
         <f>E4*F4*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>352.46399999999994</v>
+        <v>366.57599999999996</v>
       </c>
       <c r="H4" s="7">
         <f>GiaDinh!$C$21</f>
@@ -6525,35 +6525,35 @@
       </c>
       <c r="L4" s="7">
         <f t="shared" ref="L4:L67" si="1">MAX(1,ROUNDUP(G4/K4-0.0005,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="12">
         <f t="shared" ref="M4:M67" si="2">L4*I4</f>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N4" s="7">
         <f>L4*ROUNDUP(I4/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O4" s="7">
         <f>L4*(ROUNDUP(I4/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P4" s="7">
         <f t="shared" ref="P4:P67" si="3">L4*J4</f>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q4" s="7">
         <f t="shared" ref="Q4:Q67" si="4">2*P4</f>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="R4" s="7">
         <f t="shared" ref="R4:R67" si="5">P4</f>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S4" s="13">
         <f>M4*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -6573,11 +6573,11 @@
         <v>4</v>
       </c>
       <c r="F5" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G5" s="12">
         <f>E5*F5*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>352.46399999999994</v>
+        <v>366.57599999999996</v>
       </c>
       <c r="H5" s="7">
         <f>GiaDinh!$C$21</f>
@@ -6597,35 +6597,35 @@
       </c>
       <c r="L5" s="7">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N5" s="7">
         <f>L5*ROUNDUP(I5/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O5" s="7">
         <f>L5*(ROUNDUP(I5/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P5" s="7">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" si="4"/>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="R5" s="7">
         <f t="shared" si="5"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S5" s="13">
         <f>M5*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -6645,11 +6645,11 @@
         <v>2</v>
       </c>
       <c r="F6" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G6" s="12">
         <f>E6*F6*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H6" s="7">
         <f>GiaDinh!$C$21</f>
@@ -6669,35 +6669,35 @@
       </c>
       <c r="L6" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N6" s="7">
         <f>L6*ROUNDUP(I6/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O6" s="7">
         <f>L6*(ROUNDUP(I6/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P6" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q6" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R6" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S6" s="13">
         <f>M6*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -6717,11 +6717,11 @@
         <v>2</v>
       </c>
       <c r="F7" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G7" s="12">
         <f>E7*F7*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H7" s="7">
         <f>GiaDinh!$C$21</f>
@@ -6741,35 +6741,35 @@
       </c>
       <c r="L7" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N7" s="7">
         <f>L7*ROUNDUP(I7/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O7" s="7">
         <f>L7*(ROUNDUP(I7/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P7" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R7" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S7" s="13">
         <f>M7*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -6789,11 +6789,11 @@
         <v>2</v>
       </c>
       <c r="F8" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G8" s="12">
         <f>E8*F8*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H8" s="7">
         <f>GiaDinh!$C$21</f>
@@ -6813,35 +6813,35 @@
       </c>
       <c r="L8" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N8" s="7">
         <f>L8*ROUNDUP(I8/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O8" s="7">
         <f>L8*(ROUNDUP(I8/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R8" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S8" s="13">
         <f>M8*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -6861,11 +6861,11 @@
         <v>2</v>
       </c>
       <c r="F9" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G9" s="12">
         <f>E9*F9*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H9" s="7">
         <f>GiaDinh!$C$21</f>
@@ -6885,35 +6885,35 @@
       </c>
       <c r="L9" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N9" s="7">
         <f>L9*ROUNDUP(I9/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O9" s="7">
         <f>L9*(ROUNDUP(I9/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R9" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S9" s="13">
         <f>M9*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -6933,11 +6933,11 @@
         <v>2</v>
       </c>
       <c r="F10" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G10" s="12">
         <f>E10*F10*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H10" s="7">
         <f>GiaDinh!$C$21</f>
@@ -6957,35 +6957,35 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N10" s="7">
         <f>L10*ROUNDUP(I10/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O10" s="7">
         <f>L10*(ROUNDUP(I10/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q10" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R10" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S10" s="13">
         <f>M10*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7005,11 +7005,11 @@
         <v>2</v>
       </c>
       <c r="F11" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G11" s="12">
         <f>E11*F11*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H11" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7029,35 +7029,35 @@
       </c>
       <c r="L11" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N11" s="7">
         <f>L11*ROUNDUP(I11/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O11" s="7">
         <f>L11*(ROUNDUP(I11/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q11" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R11" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S11" s="13">
         <f>M11*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7077,11 +7077,11 @@
         <v>2</v>
       </c>
       <c r="F12" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G12" s="12">
         <f>E12*F12*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H12" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7101,35 +7101,35 @@
       </c>
       <c r="L12" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N12" s="7">
         <f>L12*ROUNDUP(I12/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O12" s="7">
         <f>L12*(ROUNDUP(I12/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q12" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R12" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S12" s="13">
         <f>M12*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7149,11 +7149,11 @@
         <v>2</v>
       </c>
       <c r="F13" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G13" s="12">
         <f>E13*F13*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H13" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7173,35 +7173,35 @@
       </c>
       <c r="L13" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N13" s="7">
         <f>L13*ROUNDUP(I13/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O13" s="7">
         <f>L13*(ROUNDUP(I13/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q13" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R13" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S13" s="13">
         <f>M13*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7221,11 +7221,11 @@
         <v>2</v>
       </c>
       <c r="F14" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G14" s="12">
         <f>E14*F14*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H14" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7245,35 +7245,35 @@
       </c>
       <c r="L14" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N14" s="7">
         <f>L14*ROUNDUP(I14/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O14" s="7">
         <f>L14*(ROUNDUP(I14/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q14" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R14" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S14" s="13">
         <f>M14*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7293,11 +7293,11 @@
         <v>2</v>
       </c>
       <c r="F15" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G15" s="12">
         <f>E15*F15*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H15" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7317,35 +7317,35 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N15" s="7">
         <f>L15*ROUNDUP(I15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O15" s="7">
         <f>L15*(ROUNDUP(I15/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q15" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R15" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S15" s="13">
         <f>M15*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7365,11 +7365,11 @@
         <v>2</v>
       </c>
       <c r="F16" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G16" s="12">
         <f>E16*F16*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H16" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7389,35 +7389,35 @@
       </c>
       <c r="L16" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N16" s="7">
         <f>L16*ROUNDUP(I16/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O16" s="7">
         <f>L16*(ROUNDUP(I16/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q16" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R16" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S16" s="13">
         <f>M16*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7437,11 +7437,11 @@
         <v>2</v>
       </c>
       <c r="F17" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G17" s="12">
         <f>E17*F17*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H17" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7461,35 +7461,35 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N17" s="7">
         <f>L17*ROUNDUP(I17/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O17" s="7">
         <f>L17*(ROUNDUP(I17/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R17" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S17" s="13">
         <f>M17*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7509,11 +7509,11 @@
         <v>2</v>
       </c>
       <c r="F18" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G18" s="12">
         <f>E18*F18*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H18" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7533,35 +7533,35 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N18" s="7">
         <f>L18*ROUNDUP(I18/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O18" s="7">
         <f>L18*(ROUNDUP(I18/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q18" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R18" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S18" s="13">
         <f>M18*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7581,11 +7581,11 @@
         <v>2</v>
       </c>
       <c r="F19" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G19" s="12">
         <f>E19*F19*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H19" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7605,35 +7605,35 @@
       </c>
       <c r="L19" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M19" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N19" s="7">
         <f>L19*ROUNDUP(I19/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O19" s="7">
         <f>L19*(ROUNDUP(I19/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P19" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q19" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R19" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S19" s="13">
         <f>M19*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7653,11 +7653,11 @@
         <v>2</v>
       </c>
       <c r="F20" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G20" s="12">
         <f>E20*F20*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H20" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7677,35 +7677,35 @@
       </c>
       <c r="L20" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N20" s="7">
         <f>L20*ROUNDUP(I20/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O20" s="7">
         <f>L20*(ROUNDUP(I20/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P20" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q20" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R20" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S20" s="13">
         <f>M20*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -7725,11 +7725,11 @@
         <v>2</v>
       </c>
       <c r="F21" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G21" s="12">
         <f>E21*F21*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>176.23199999999997</v>
+        <v>183.28799999999998</v>
       </c>
       <c r="H21" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7749,35 +7749,35 @@
       </c>
       <c r="L21" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" s="12">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N21" s="7">
         <f>L21*ROUNDUP(I21/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O21" s="7">
         <f>L21*(ROUNDUP(I21/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P21" s="7">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q21" s="7">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R21" s="7">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S21" s="13">
         <f>M21*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -7797,11 +7797,11 @@
         <v>1</v>
       </c>
       <c r="F22" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G22" s="12">
         <f>E22*F22*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H22" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7821,35 +7821,35 @@
       </c>
       <c r="L22" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N22" s="7">
         <f>L22*ROUNDUP(I22/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O22" s="7">
         <f>L22*(ROUNDUP(I22/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P22" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q22" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R22" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S22" s="13">
         <f>M22*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -7869,11 +7869,11 @@
         <v>1</v>
       </c>
       <c r="F23" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G23" s="12">
         <f>E23*F23*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H23" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7893,35 +7893,35 @@
       </c>
       <c r="L23" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N23" s="7">
         <f>L23*ROUNDUP(I23/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O23" s="7">
         <f>L23*(ROUNDUP(I23/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P23" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q23" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R23" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S23" s="13">
         <f>M23*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -7941,11 +7941,11 @@
         <v>1</v>
       </c>
       <c r="F24" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G24" s="12">
         <f>E24*F24*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H24" s="7">
         <f>GiaDinh!$C$21</f>
@@ -7965,35 +7965,35 @@
       </c>
       <c r="L24" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N24" s="7">
         <f>L24*ROUNDUP(I24/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O24" s="7">
         <f>L24*(ROUNDUP(I24/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P24" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q24" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R24" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S24" s="13">
         <f>M24*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8013,11 +8013,11 @@
         <v>1</v>
       </c>
       <c r="F25" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G25" s="12">
         <f>E25*F25*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H25" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8037,35 +8037,35 @@
       </c>
       <c r="L25" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N25" s="7">
         <f>L25*ROUNDUP(I25/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O25" s="7">
         <f>L25*(ROUNDUP(I25/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P25" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q25" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R25" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S25" s="13">
         <f>M25*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8085,11 +8085,11 @@
         <v>1</v>
       </c>
       <c r="F26" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G26" s="12">
         <f>E26*F26*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H26" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8109,35 +8109,35 @@
       </c>
       <c r="L26" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N26" s="7">
         <f>L26*ROUNDUP(I26/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O26" s="7">
         <f>L26*(ROUNDUP(I26/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P26" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q26" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R26" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S26" s="13">
         <f>M26*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8157,11 +8157,11 @@
         <v>1</v>
       </c>
       <c r="F27" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G27" s="12">
         <f>E27*F27*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H27" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8181,35 +8181,35 @@
       </c>
       <c r="L27" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N27" s="7">
         <f>L27*ROUNDUP(I27/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O27" s="7">
         <f>L27*(ROUNDUP(I27/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P27" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q27" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R27" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S27" s="13">
         <f>M27*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8229,11 +8229,11 @@
         <v>1</v>
       </c>
       <c r="F28" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G28" s="12">
         <f>E28*F28*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H28" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8253,35 +8253,35 @@
       </c>
       <c r="L28" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N28" s="7">
         <f>L28*ROUNDUP(I28/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O28" s="7">
         <f>L28*(ROUNDUP(I28/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P28" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q28" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R28" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S28" s="13">
         <f>M28*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8301,11 +8301,11 @@
         <v>1</v>
       </c>
       <c r="F29" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G29" s="12">
         <f>E29*F29*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H29" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8325,35 +8325,35 @@
       </c>
       <c r="L29" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N29" s="7">
         <f>L29*ROUNDUP(I29/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O29" s="7">
         <f>L29*(ROUNDUP(I29/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P29" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q29" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R29" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S29" s="13">
         <f>M29*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8373,11 +8373,11 @@
         <v>1</v>
       </c>
       <c r="F30" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G30" s="12">
         <f>E30*F30*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H30" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8397,35 +8397,35 @@
       </c>
       <c r="L30" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N30" s="7">
         <f>L30*ROUNDUP(I30/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O30" s="7">
         <f>L30*(ROUNDUP(I30/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P30" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q30" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R30" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S30" s="13">
         <f>M30*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8445,11 +8445,11 @@
         <v>1</v>
       </c>
       <c r="F31" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G31" s="12">
         <f>E31*F31*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H31" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8469,35 +8469,35 @@
       </c>
       <c r="L31" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N31" s="7">
         <f>L31*ROUNDUP(I31/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O31" s="7">
         <f>L31*(ROUNDUP(I31/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P31" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q31" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R31" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S31" s="13">
         <f>M31*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8517,11 +8517,11 @@
         <v>1</v>
       </c>
       <c r="F32" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G32" s="12">
         <f>E32*F32*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H32" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8541,35 +8541,35 @@
       </c>
       <c r="L32" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N32" s="7">
         <f>L32*ROUNDUP(I32/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O32" s="7">
         <f>L32*(ROUNDUP(I32/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P32" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q32" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R32" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S32" s="13">
         <f>M32*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8589,11 +8589,11 @@
         <v>1</v>
       </c>
       <c r="F33" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G33" s="12">
         <f>E33*F33*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H33" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8613,35 +8613,35 @@
       </c>
       <c r="L33" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N33" s="7">
         <f>L33*ROUNDUP(I33/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O33" s="7">
         <f>L33*(ROUNDUP(I33/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P33" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q33" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R33" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S33" s="13">
         <f>M33*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8661,11 +8661,11 @@
         <v>1</v>
       </c>
       <c r="F34" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G34" s="12">
         <f>E34*F34*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H34" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8685,35 +8685,35 @@
       </c>
       <c r="L34" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N34" s="7">
         <f>L34*ROUNDUP(I34/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O34" s="7">
         <f>L34*(ROUNDUP(I34/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P34" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q34" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R34" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S34" s="13">
         <f>M34*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8733,11 +8733,11 @@
         <v>1</v>
       </c>
       <c r="F35" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G35" s="12">
         <f>E35*F35*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H35" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8757,35 +8757,35 @@
       </c>
       <c r="L35" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M35" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N35" s="7">
         <f>L35*ROUNDUP(I35/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O35" s="7">
         <f>L35*(ROUNDUP(I35/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P35" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q35" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R35" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S35" s="13">
         <f>M35*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8805,11 +8805,11 @@
         <v>1</v>
       </c>
       <c r="F36" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G36" s="12">
         <f>E36*F36*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H36" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8829,35 +8829,35 @@
       </c>
       <c r="L36" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N36" s="7">
         <f>L36*ROUNDUP(I36/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O36" s="7">
         <f>L36*(ROUNDUP(I36/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P36" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R36" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S36" s="13">
         <f>M36*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8877,11 +8877,11 @@
         <v>1</v>
       </c>
       <c r="F37" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G37" s="12">
         <f>E37*F37*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H37" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8901,35 +8901,35 @@
       </c>
       <c r="L37" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N37" s="7">
         <f>L37*ROUNDUP(I37/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O37" s="7">
         <f>L37*(ROUNDUP(I37/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P37" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q37" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R37" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S37" s="13">
         <f>M37*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -8949,11 +8949,11 @@
         <v>1</v>
       </c>
       <c r="F38" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G38" s="12">
         <f>E38*F38*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H38" s="7">
         <f>GiaDinh!$C$21</f>
@@ -8973,35 +8973,35 @@
       </c>
       <c r="L38" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N38" s="7">
         <f>L38*ROUNDUP(I38/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O38" s="7">
         <f>L38*(ROUNDUP(I38/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P38" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q38" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R38" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S38" s="13">
         <f>M38*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9021,11 +9021,11 @@
         <v>1</v>
       </c>
       <c r="F39" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G39" s="12">
         <f>E39*F39*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H39" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9045,35 +9045,35 @@
       </c>
       <c r="L39" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N39" s="7">
         <f>L39*ROUNDUP(I39/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O39" s="7">
         <f>L39*(ROUNDUP(I39/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P39" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q39" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R39" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S39" s="13">
         <f>M39*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9093,11 +9093,11 @@
         <v>1</v>
       </c>
       <c r="F40" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G40" s="12">
         <f>E40*F40*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H40" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9117,35 +9117,35 @@
       </c>
       <c r="L40" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N40" s="7">
         <f>L40*ROUNDUP(I40/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O40" s="7">
         <f>L40*(ROUNDUP(I40/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P40" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q40" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R40" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S40" s="13">
         <f>M40*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9165,11 +9165,11 @@
         <v>1</v>
       </c>
       <c r="F41" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G41" s="12">
         <f>E41*F41*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H41" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9189,35 +9189,35 @@
       </c>
       <c r="L41" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N41" s="7">
         <f>L41*ROUNDUP(I41/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O41" s="7">
         <f>L41*(ROUNDUP(I41/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P41" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q41" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R41" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S41" s="13">
         <f>M41*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9237,11 +9237,11 @@
         <v>1</v>
       </c>
       <c r="F42" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G42" s="12">
         <f>E42*F42*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H42" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9261,35 +9261,35 @@
       </c>
       <c r="L42" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N42" s="7">
         <f>L42*ROUNDUP(I42/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O42" s="7">
         <f>L42*(ROUNDUP(I42/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P42" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q42" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R42" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S42" s="13">
         <f>M42*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9309,11 +9309,11 @@
         <v>1</v>
       </c>
       <c r="F43" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G43" s="12">
         <f>E43*F43*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H43" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9333,35 +9333,35 @@
       </c>
       <c r="L43" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N43" s="7">
         <f>L43*ROUNDUP(I43/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O43" s="7">
         <f>L43*(ROUNDUP(I43/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P43" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q43" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R43" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S43" s="13">
         <f>M43*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9381,11 +9381,11 @@
         <v>1</v>
       </c>
       <c r="F44" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G44" s="12">
         <f>E44*F44*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H44" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9405,35 +9405,35 @@
       </c>
       <c r="L44" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N44" s="7">
         <f>L44*ROUNDUP(I44/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O44" s="7">
         <f>L44*(ROUNDUP(I44/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P44" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q44" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R44" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S44" s="13">
         <f>M44*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9453,11 +9453,11 @@
         <v>1</v>
       </c>
       <c r="F45" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G45" s="12">
         <f>E45*F45*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H45" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9477,35 +9477,35 @@
       </c>
       <c r="L45" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M45" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N45" s="7">
         <f>L45*ROUNDUP(I45/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O45" s="7">
         <f>L45*(ROUNDUP(I45/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P45" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q45" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R45" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S45" s="13">
         <f>M45*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9525,11 +9525,11 @@
         <v>1</v>
       </c>
       <c r="F46" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G46" s="12">
         <f>E46*F46*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H46" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9549,35 +9549,35 @@
       </c>
       <c r="L46" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N46" s="7">
         <f>L46*ROUNDUP(I46/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O46" s="7">
         <f>L46*(ROUNDUP(I46/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P46" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q46" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R46" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S46" s="13">
         <f>M46*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9597,11 +9597,11 @@
         <v>1</v>
       </c>
       <c r="F47" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G47" s="12">
         <f>E47*F47*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H47" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9621,35 +9621,35 @@
       </c>
       <c r="L47" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M47" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N47" s="7">
         <f>L47*ROUNDUP(I47/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O47" s="7">
         <f>L47*(ROUNDUP(I47/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P47" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q47" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R47" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S47" s="13">
         <f>M47*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9669,11 +9669,11 @@
         <v>1</v>
       </c>
       <c r="F48" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G48" s="12">
         <f>E48*F48*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H48" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9693,35 +9693,35 @@
       </c>
       <c r="L48" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N48" s="7">
         <f>L48*ROUNDUP(I48/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O48" s="7">
         <f>L48*(ROUNDUP(I48/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P48" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q48" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R48" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S48" s="13">
         <f>M48*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9741,11 +9741,11 @@
         <v>1</v>
       </c>
       <c r="F49" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G49" s="12">
         <f>E49*F49*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H49" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9765,35 +9765,35 @@
       </c>
       <c r="L49" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N49" s="7">
         <f>L49*ROUNDUP(I49/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O49" s="7">
         <f>L49*(ROUNDUP(I49/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P49" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q49" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R49" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S49" s="13">
         <f>M49*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9813,11 +9813,11 @@
         <v>1</v>
       </c>
       <c r="F50" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G50" s="12">
         <f>E50*F50*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H50" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9837,35 +9837,35 @@
       </c>
       <c r="L50" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N50" s="7">
         <f>L50*ROUNDUP(I50/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O50" s="7">
         <f>L50*(ROUNDUP(I50/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P50" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q50" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R50" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S50" s="13">
         <f>M50*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -9885,11 +9885,11 @@
         <v>1</v>
       </c>
       <c r="F51" s="7">
-        <v>104.9</v>
+        <v>109.1</v>
       </c>
       <c r="G51" s="12">
         <f>E51*F51*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>88.115999999999985</v>
+        <v>91.643999999999991</v>
       </c>
       <c r="H51" s="7">
         <f>GiaDinh!$C$21</f>
@@ -9909,35 +9909,35 @@
       </c>
       <c r="L51" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M51" s="12">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N51" s="7">
         <f>L51*ROUNDUP(I51/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O51" s="7">
         <f>L51*(ROUNDUP(I51/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P51" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q51" s="7">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R51" s="7">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S51" s="13">
         <f>M51*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="52" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -21621,11 +21621,11 @@
         <v>4</v>
       </c>
       <c r="F214" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G214" s="12">
         <f>E214*F214*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>252</v>
+        <v>198.57599999999999</v>
       </c>
       <c r="H214" s="7">
         <f>GiaDinh!$C$21</f>
@@ -21693,11 +21693,11 @@
         <v>4</v>
       </c>
       <c r="F215" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G215" s="12">
         <f>E215*F215*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>252</v>
+        <v>198.57599999999999</v>
       </c>
       <c r="H215" s="7">
         <f>GiaDinh!$C$21</f>
@@ -21765,11 +21765,11 @@
         <v>6</v>
       </c>
       <c r="F216" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G216" s="12">
         <f>E216*F216*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>378</v>
+        <v>297.86399999999998</v>
       </c>
       <c r="H216" s="7">
         <f>GiaDinh!$C$21</f>
@@ -21789,35 +21789,35 @@
       </c>
       <c r="L216" s="7">
         <f t="shared" si="19"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M216" s="12">
         <f t="shared" si="20"/>
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N216" s="7">
         <f>L216*ROUNDUP(I216/GiaDinh!$C$5-0.0005,0)</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O216" s="7">
         <f>L216*(ROUNDUP(I216/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P216" s="7">
         <f t="shared" si="21"/>
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="Q216" s="7">
         <f t="shared" si="22"/>
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="R216" s="7">
         <f t="shared" si="23"/>
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="S216" s="13">
         <f>M216*GiaDinh!$C$7</f>
-        <v>225.74999999999997</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="217" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -21837,11 +21837,11 @@
         <v>1</v>
       </c>
       <c r="F217" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G217" s="12">
         <f>E217*F217*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H217" s="7">
         <f>GiaDinh!$C$21</f>
@@ -21909,11 +21909,11 @@
         <v>1</v>
       </c>
       <c r="F218" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G218" s="12">
         <f>E218*F218*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H218" s="7">
         <f>GiaDinh!$C$21</f>
@@ -21981,11 +21981,11 @@
         <v>1</v>
       </c>
       <c r="F219" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G219" s="12">
         <f>E219*F219*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H219" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22053,11 +22053,11 @@
         <v>1</v>
       </c>
       <c r="F220" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G220" s="12">
         <f>E220*F220*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H220" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22125,11 +22125,11 @@
         <v>1</v>
       </c>
       <c r="F221" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G221" s="12">
         <f>E221*F221*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H221" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22197,11 +22197,11 @@
         <v>1</v>
       </c>
       <c r="F222" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G222" s="12">
         <f>E222*F222*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H222" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22269,11 +22269,11 @@
         <v>1</v>
       </c>
       <c r="F223" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G223" s="12">
         <f>E223*F223*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H223" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22341,11 +22341,11 @@
         <v>1</v>
       </c>
       <c r="F224" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G224" s="12">
         <f>E224*F224*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H224" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22413,11 +22413,11 @@
         <v>1</v>
       </c>
       <c r="F225" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G225" s="12">
         <f>E225*F225*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H225" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22485,11 +22485,11 @@
         <v>1</v>
       </c>
       <c r="F226" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G226" s="12">
         <f>E226*F226*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H226" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22557,11 +22557,11 @@
         <v>1</v>
       </c>
       <c r="F227" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G227" s="12">
         <f>E227*F227*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H227" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22629,11 +22629,11 @@
         <v>1</v>
       </c>
       <c r="F228" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G228" s="12">
         <f>E228*F228*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H228" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22701,11 +22701,11 @@
         <v>1</v>
       </c>
       <c r="F229" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G229" s="12">
         <f>E229*F229*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H229" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22773,11 +22773,11 @@
         <v>1</v>
       </c>
       <c r="F230" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G230" s="12">
         <f>E230*F230*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H230" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22845,11 +22845,11 @@
         <v>1</v>
       </c>
       <c r="F231" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G231" s="12">
         <f>E231*F231*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H231" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22917,11 +22917,11 @@
         <v>1</v>
       </c>
       <c r="F232" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G232" s="12">
         <f>E232*F232*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H232" s="7">
         <f>GiaDinh!$C$21</f>
@@ -22989,11 +22989,11 @@
         <v>1</v>
       </c>
       <c r="F233" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G233" s="12">
         <f>E233*F233*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H233" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23061,11 +23061,11 @@
         <v>1</v>
       </c>
       <c r="F234" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G234" s="12">
         <f>E234*F234*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H234" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23133,11 +23133,11 @@
         <v>1</v>
       </c>
       <c r="F235" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G235" s="12">
         <f>E235*F235*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H235" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23205,11 +23205,11 @@
         <v>1</v>
       </c>
       <c r="F236" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G236" s="12">
         <f>E236*F236*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H236" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23277,11 +23277,11 @@
         <v>1</v>
       </c>
       <c r="F237" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G237" s="12">
         <f>E237*F237*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H237" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23349,11 +23349,11 @@
         <v>1</v>
       </c>
       <c r="F238" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G238" s="12">
         <f>E238*F238*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H238" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23421,11 +23421,11 @@
         <v>1</v>
       </c>
       <c r="F239" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G239" s="12">
         <f>E239*F239*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H239" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23493,11 +23493,11 @@
         <v>1</v>
       </c>
       <c r="F240" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G240" s="12">
         <f>E240*F240*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H240" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23565,11 +23565,11 @@
         <v>1</v>
       </c>
       <c r="F241" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G241" s="12">
         <f>E241*F241*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H241" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23637,11 +23637,11 @@
         <v>1</v>
       </c>
       <c r="F242" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G242" s="12">
         <f>E242*F242*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H242" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23709,11 +23709,11 @@
         <v>1</v>
       </c>
       <c r="F243" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G243" s="12">
         <f>E243*F243*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H243" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23781,11 +23781,11 @@
         <v>1</v>
       </c>
       <c r="F244" s="7">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="G244" s="12">
         <f>E244*F244*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>63</v>
+        <v>49.643999999999998</v>
       </c>
       <c r="H244" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23853,11 +23853,11 @@
         <v>2</v>
       </c>
       <c r="F245" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G245" s="12">
         <f>E245*F245*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>92.231999999999999</v>
+        <v>80.47199999999998</v>
       </c>
       <c r="H245" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23877,35 +23877,35 @@
       </c>
       <c r="L245" s="7">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M245" s="12">
         <f t="shared" si="20"/>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N245" s="7">
         <f>L245*ROUNDUP(I245/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O245" s="7">
         <f>L245*(ROUNDUP(I245/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P245" s="7">
         <f t="shared" si="21"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q245" s="7">
         <f t="shared" si="22"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R245" s="7">
         <f t="shared" si="23"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S245" s="13">
         <f>M245*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="246" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -23925,11 +23925,11 @@
         <v>2</v>
       </c>
       <c r="F246" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G246" s="12">
         <f>E246*F246*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>92.231999999999999</v>
+        <v>80.47199999999998</v>
       </c>
       <c r="H246" s="7">
         <f>GiaDinh!$C$21</f>
@@ -23949,35 +23949,35 @@
       </c>
       <c r="L246" s="7">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M246" s="12">
         <f t="shared" si="20"/>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N246" s="7">
         <f>L246*ROUNDUP(I246/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O246" s="7">
         <f>L246*(ROUNDUP(I246/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P246" s="7">
         <f t="shared" si="21"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q246" s="7">
         <f t="shared" si="22"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R246" s="7">
         <f t="shared" si="23"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S246" s="13">
         <f>M246*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="247" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -23997,11 +23997,11 @@
         <v>3</v>
       </c>
       <c r="F247" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G247" s="12">
         <f>E247*F247*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>138.34799999999996</v>
+        <v>120.70799999999998</v>
       </c>
       <c r="H247" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24069,11 +24069,11 @@
         <v>5</v>
       </c>
       <c r="F248" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G248" s="12">
         <f>E248*F248*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>230.57999999999996</v>
+        <v>201.17999999999998</v>
       </c>
       <c r="H248" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24141,11 +24141,11 @@
         <v>3</v>
       </c>
       <c r="F249" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G249" s="12">
         <f>E249*F249*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>138.34799999999996</v>
+        <v>120.70799999999998</v>
       </c>
       <c r="H249" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24213,11 +24213,11 @@
         <v>1</v>
       </c>
       <c r="F250" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G250" s="12">
         <f>E250*F250*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H250" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24285,11 +24285,11 @@
         <v>3</v>
       </c>
       <c r="F251" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G251" s="12">
         <f>E251*F251*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>138.34799999999996</v>
+        <v>120.70799999999998</v>
       </c>
       <c r="H251" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24357,11 +24357,11 @@
         <v>3</v>
       </c>
       <c r="F252" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G252" s="12">
         <f>E252*F252*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>138.34799999999996</v>
+        <v>120.70799999999998</v>
       </c>
       <c r="H252" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24429,11 +24429,11 @@
         <v>1</v>
       </c>
       <c r="F253" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G253" s="12">
         <f>E253*F253*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H253" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24501,11 +24501,11 @@
         <v>1</v>
       </c>
       <c r="F254" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G254" s="12">
         <f>E254*F254*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H254" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24573,11 +24573,11 @@
         <v>1</v>
       </c>
       <c r="F255" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G255" s="12">
         <f>E255*F255*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H255" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24645,11 +24645,11 @@
         <v>1</v>
       </c>
       <c r="F256" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G256" s="12">
         <f>E256*F256*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H256" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24717,11 +24717,11 @@
         <v>1</v>
       </c>
       <c r="F257" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G257" s="12">
         <f>E257*F257*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H257" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24789,11 +24789,11 @@
         <v>1</v>
       </c>
       <c r="F258" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G258" s="12">
         <f>E258*F258*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H258" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24861,11 +24861,11 @@
         <v>1</v>
       </c>
       <c r="F259" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G259" s="12">
         <f>E259*F259*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H259" s="7">
         <f>GiaDinh!$C$21</f>
@@ -24933,11 +24933,11 @@
         <v>1</v>
       </c>
       <c r="F260" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G260" s="12">
         <f>E260*F260*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H260" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25005,11 +25005,11 @@
         <v>1</v>
       </c>
       <c r="F261" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G261" s="12">
         <f>E261*F261*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H261" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25077,11 +25077,11 @@
         <v>1</v>
       </c>
       <c r="F262" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G262" s="12">
         <f>E262*F262*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H262" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25149,11 +25149,11 @@
         <v>1</v>
       </c>
       <c r="F263" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G263" s="12">
         <f>E263*F263*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H263" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25221,11 +25221,11 @@
         <v>1</v>
       </c>
       <c r="F264" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G264" s="12">
         <f>E264*F264*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H264" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25293,11 +25293,11 @@
         <v>1</v>
       </c>
       <c r="F265" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G265" s="12">
         <f>E265*F265*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H265" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25365,11 +25365,11 @@
         <v>1</v>
       </c>
       <c r="F266" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G266" s="12">
         <f>E266*F266*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H266" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25437,11 +25437,11 @@
         <v>1</v>
       </c>
       <c r="F267" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G267" s="12">
         <f>E267*F267*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H267" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25509,11 +25509,11 @@
         <v>1</v>
       </c>
       <c r="F268" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G268" s="12">
         <f>E268*F268*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H268" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25581,11 +25581,11 @@
         <v>1</v>
       </c>
       <c r="F269" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G269" s="12">
         <f>E269*F269*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H269" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25653,11 +25653,11 @@
         <v>1</v>
       </c>
       <c r="F270" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G270" s="12">
         <f>E270*F270*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H270" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25725,11 +25725,11 @@
         <v>1</v>
       </c>
       <c r="F271" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G271" s="12">
         <f>E271*F271*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H271" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25797,11 +25797,11 @@
         <v>1</v>
       </c>
       <c r="F272" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G272" s="12">
         <f>E272*F272*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H272" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25869,11 +25869,11 @@
         <v>1</v>
       </c>
       <c r="F273" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G273" s="12">
         <f>E273*F273*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H273" s="7">
         <f>GiaDinh!$C$21</f>
@@ -25941,11 +25941,11 @@
         <v>1</v>
       </c>
       <c r="F274" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G274" s="12">
         <f>E274*F274*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H274" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26013,11 +26013,11 @@
         <v>1</v>
       </c>
       <c r="F275" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G275" s="12">
         <f>E275*F275*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H275" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26085,11 +26085,11 @@
         <v>1</v>
       </c>
       <c r="F276" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G276" s="12">
         <f>E276*F276*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H276" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26157,11 +26157,11 @@
         <v>1</v>
       </c>
       <c r="F277" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G277" s="12">
         <f>E277*F277*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H277" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26229,11 +26229,11 @@
         <v>1</v>
       </c>
       <c r="F278" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G278" s="12">
         <f>E278*F278*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H278" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26301,11 +26301,11 @@
         <v>1</v>
       </c>
       <c r="F279" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G279" s="12">
         <f>E279*F279*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H279" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26373,11 +26373,11 @@
         <v>1</v>
       </c>
       <c r="F280" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G280" s="12">
         <f>E280*F280*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H280" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26445,11 +26445,11 @@
         <v>1</v>
       </c>
       <c r="F281" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G281" s="12">
         <f>E281*F281*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H281" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26517,11 +26517,11 @@
         <v>1</v>
       </c>
       <c r="F282" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G282" s="12">
         <f>E282*F282*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H282" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26589,11 +26589,11 @@
         <v>1</v>
       </c>
       <c r="F283" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G283" s="12">
         <f>E283*F283*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H283" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26661,11 +26661,11 @@
         <v>1</v>
       </c>
       <c r="F284" s="7">
-        <v>54.9</v>
+        <v>47.9</v>
       </c>
       <c r="G284" s="12">
         <f>E284*F284*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>46.116</v>
+        <v>40.23599999999999</v>
       </c>
       <c r="H284" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26733,11 +26733,11 @@
         <v>4</v>
       </c>
       <c r="F285" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G285" s="12">
         <f>E285*F285*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>359.51999999999992</v>
+        <v>376.99199999999996</v>
       </c>
       <c r="H285" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26757,35 +26757,35 @@
       </c>
       <c r="L285" s="7">
         <f t="shared" si="25"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M285" s="12">
         <f t="shared" si="26"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N285" s="7">
         <f>L285*ROUNDUP(I285/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O285" s="7">
         <f>L285*(ROUNDUP(I285/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P285" s="7">
         <f t="shared" si="27"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q285" s="7">
         <f t="shared" si="28"/>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="R285" s="7">
         <f t="shared" si="29"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S285" s="13">
         <f>M285*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="286" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -26805,11 +26805,11 @@
         <v>2</v>
       </c>
       <c r="F286" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G286" s="12">
         <f>E286*F286*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H286" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26829,35 +26829,35 @@
       </c>
       <c r="L286" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M286" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N286" s="7">
         <f>L286*ROUNDUP(I286/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O286" s="7">
         <f>L286*(ROUNDUP(I286/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P286" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q286" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R286" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S286" s="13">
         <f>M286*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="287" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -26877,11 +26877,11 @@
         <v>2</v>
       </c>
       <c r="F287" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G287" s="12">
         <f>E287*F287*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H287" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26901,35 +26901,35 @@
       </c>
       <c r="L287" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M287" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N287" s="7">
         <f>L287*ROUNDUP(I287/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O287" s="7">
         <f>L287*(ROUNDUP(I287/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P287" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q287" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R287" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S287" s="13">
         <f>M287*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="288" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -26949,11 +26949,11 @@
         <v>2</v>
       </c>
       <c r="F288" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G288" s="12">
         <f>E288*F288*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H288" s="7">
         <f>GiaDinh!$C$21</f>
@@ -26973,35 +26973,35 @@
       </c>
       <c r="L288" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M288" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N288" s="7">
         <f>L288*ROUNDUP(I288/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O288" s="7">
         <f>L288*(ROUNDUP(I288/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P288" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q288" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R288" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S288" s="13">
         <f>M288*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="289" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27021,11 +27021,11 @@
         <v>4</v>
       </c>
       <c r="F289" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G289" s="12">
         <f>E289*F289*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>359.51999999999992</v>
+        <v>376.99199999999996</v>
       </c>
       <c r="H289" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27045,35 +27045,35 @@
       </c>
       <c r="L289" s="7">
         <f t="shared" si="25"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M289" s="12">
         <f t="shared" si="26"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N289" s="7">
         <f>L289*ROUNDUP(I289/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O289" s="7">
         <f>L289*(ROUNDUP(I289/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P289" s="7">
         <f t="shared" si="27"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q289" s="7">
         <f t="shared" si="28"/>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="R289" s="7">
         <f t="shared" si="29"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S289" s="13">
         <f>M289*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="290" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27093,11 +27093,11 @@
         <v>4</v>
       </c>
       <c r="F290" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G290" s="12">
         <f>E290*F290*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>359.51999999999992</v>
+        <v>376.99199999999996</v>
       </c>
       <c r="H290" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27117,35 +27117,35 @@
       </c>
       <c r="L290" s="7">
         <f t="shared" si="25"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M290" s="12">
         <f t="shared" si="26"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N290" s="7">
         <f>L290*ROUNDUP(I290/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O290" s="7">
         <f>L290*(ROUNDUP(I290/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P290" s="7">
         <f t="shared" si="27"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q290" s="7">
         <f t="shared" si="28"/>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="R290" s="7">
         <f t="shared" si="29"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S290" s="13">
         <f>M290*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="291" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27165,11 +27165,11 @@
         <v>2</v>
       </c>
       <c r="F291" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G291" s="12">
         <f>E291*F291*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H291" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27189,35 +27189,35 @@
       </c>
       <c r="L291" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M291" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N291" s="7">
         <f>L291*ROUNDUP(I291/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O291" s="7">
         <f>L291*(ROUNDUP(I291/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P291" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q291" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R291" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S291" s="13">
         <f>M291*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="292" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27237,11 +27237,11 @@
         <v>2</v>
       </c>
       <c r="F292" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G292" s="12">
         <f>E292*F292*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H292" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27261,35 +27261,35 @@
       </c>
       <c r="L292" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M292" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N292" s="7">
         <f>L292*ROUNDUP(I292/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O292" s="7">
         <f>L292*(ROUNDUP(I292/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P292" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q292" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R292" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S292" s="13">
         <f>M292*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="293" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27309,11 +27309,11 @@
         <v>2</v>
       </c>
       <c r="F293" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G293" s="12">
         <f>E293*F293*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H293" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27333,35 +27333,35 @@
       </c>
       <c r="L293" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M293" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N293" s="7">
         <f>L293*ROUNDUP(I293/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O293" s="7">
         <f>L293*(ROUNDUP(I293/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P293" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q293" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R293" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S293" s="13">
         <f>M293*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="294" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27381,11 +27381,11 @@
         <v>2</v>
       </c>
       <c r="F294" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G294" s="12">
         <f>E294*F294*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H294" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27405,35 +27405,35 @@
       </c>
       <c r="L294" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M294" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N294" s="7">
         <f>L294*ROUNDUP(I294/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O294" s="7">
         <f>L294*(ROUNDUP(I294/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P294" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q294" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R294" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S294" s="13">
         <f>M294*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="295" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27453,11 +27453,11 @@
         <v>2</v>
       </c>
       <c r="F295" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G295" s="12">
         <f>E295*F295*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H295" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27477,35 +27477,35 @@
       </c>
       <c r="L295" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M295" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N295" s="7">
         <f>L295*ROUNDUP(I295/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O295" s="7">
         <f>L295*(ROUNDUP(I295/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P295" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q295" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R295" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S295" s="13">
         <f>M295*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="296" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27525,11 +27525,11 @@
         <v>2</v>
       </c>
       <c r="F296" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G296" s="12">
         <f>E296*F296*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H296" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27549,35 +27549,35 @@
       </c>
       <c r="L296" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M296" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N296" s="7">
         <f>L296*ROUNDUP(I296/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O296" s="7">
         <f>L296*(ROUNDUP(I296/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P296" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q296" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R296" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S296" s="13">
         <f>M296*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="297" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27597,11 +27597,11 @@
         <v>2</v>
       </c>
       <c r="F297" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G297" s="12">
         <f>E297*F297*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H297" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27621,35 +27621,35 @@
       </c>
       <c r="L297" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M297" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N297" s="7">
         <f>L297*ROUNDUP(I297/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O297" s="7">
         <f>L297*(ROUNDUP(I297/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P297" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q297" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R297" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S297" s="13">
         <f>M297*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="298" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27669,11 +27669,11 @@
         <v>2</v>
       </c>
       <c r="F298" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G298" s="12">
         <f>E298*F298*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H298" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27693,35 +27693,35 @@
       </c>
       <c r="L298" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M298" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N298" s="7">
         <f>L298*ROUNDUP(I298/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O298" s="7">
         <f>L298*(ROUNDUP(I298/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P298" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q298" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R298" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S298" s="13">
         <f>M298*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="299" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27741,11 +27741,11 @@
         <v>4</v>
       </c>
       <c r="F299" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G299" s="12">
         <f>E299*F299*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>359.51999999999992</v>
+        <v>376.99199999999996</v>
       </c>
       <c r="H299" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27765,35 +27765,35 @@
       </c>
       <c r="L299" s="7">
         <f t="shared" si="25"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M299" s="12">
         <f t="shared" si="26"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N299" s="7">
         <f>L299*ROUNDUP(I299/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O299" s="7">
         <f>L299*(ROUNDUP(I299/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P299" s="7">
         <f t="shared" si="27"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q299" s="7">
         <f t="shared" si="28"/>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="R299" s="7">
         <f t="shared" si="29"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S299" s="13">
         <f>M299*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="300" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27813,11 +27813,11 @@
         <v>2</v>
       </c>
       <c r="F300" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G300" s="12">
         <f>E300*F300*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H300" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27837,35 +27837,35 @@
       </c>
       <c r="L300" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M300" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N300" s="7">
         <f>L300*ROUNDUP(I300/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O300" s="7">
         <f>L300*(ROUNDUP(I300/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P300" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q300" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R300" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S300" s="13">
         <f>M300*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="301" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27885,11 +27885,11 @@
         <v>4</v>
       </c>
       <c r="F301" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G301" s="12">
         <f>E301*F301*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>359.51999999999992</v>
+        <v>376.99199999999996</v>
       </c>
       <c r="H301" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27909,35 +27909,35 @@
       </c>
       <c r="L301" s="7">
         <f t="shared" si="25"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M301" s="12">
         <f t="shared" si="26"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N301" s="7">
         <f>L301*ROUNDUP(I301/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O301" s="7">
         <f>L301*(ROUNDUP(I301/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P301" s="7">
         <f t="shared" si="27"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q301" s="7">
         <f t="shared" si="28"/>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="R301" s="7">
         <f t="shared" si="29"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S301" s="13">
         <f>M301*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="302" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -27957,11 +27957,11 @@
         <v>2</v>
       </c>
       <c r="F302" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G302" s="12">
         <f>E302*F302*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H302" s="7">
         <f>GiaDinh!$C$21</f>
@@ -27981,35 +27981,35 @@
       </c>
       <c r="L302" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M302" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N302" s="7">
         <f>L302*ROUNDUP(I302/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O302" s="7">
         <f>L302*(ROUNDUP(I302/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P302" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q302" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R302" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S302" s="13">
         <f>M302*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="303" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -28029,11 +28029,11 @@
         <v>4</v>
       </c>
       <c r="F303" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G303" s="12">
         <f>E303*F303*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>359.51999999999992</v>
+        <v>376.99199999999996</v>
       </c>
       <c r="H303" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28053,35 +28053,35 @@
       </c>
       <c r="L303" s="7">
         <f t="shared" si="25"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M303" s="12">
         <f t="shared" si="26"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N303" s="7">
         <f>L303*ROUNDUP(I303/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O303" s="7">
         <f>L303*(ROUNDUP(I303/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P303" s="7">
         <f t="shared" si="27"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q303" s="7">
         <f t="shared" si="28"/>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="R303" s="7">
         <f t="shared" si="29"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S303" s="13">
         <f>M303*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="304" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -28101,11 +28101,11 @@
         <v>2</v>
       </c>
       <c r="F304" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G304" s="12">
         <f>E304*F304*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H304" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28125,35 +28125,35 @@
       </c>
       <c r="L304" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M304" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N304" s="7">
         <f>L304*ROUNDUP(I304/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O304" s="7">
         <f>L304*(ROUNDUP(I304/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P304" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q304" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R304" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S304" s="13">
         <f>M304*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="305" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -28173,11 +28173,11 @@
         <v>4</v>
       </c>
       <c r="F305" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G305" s="12">
         <f>E305*F305*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>359.51999999999992</v>
+        <v>376.99199999999996</v>
       </c>
       <c r="H305" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28197,35 +28197,35 @@
       </c>
       <c r="L305" s="7">
         <f t="shared" si="25"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M305" s="12">
         <f t="shared" si="26"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N305" s="7">
         <f>L305*ROUNDUP(I305/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O305" s="7">
         <f>L305*(ROUNDUP(I305/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P305" s="7">
         <f t="shared" si="27"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="Q305" s="7">
         <f t="shared" si="28"/>
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="R305" s="7">
         <f t="shared" si="29"/>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S305" s="13">
         <f>M305*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="306" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -28245,11 +28245,11 @@
         <v>2</v>
       </c>
       <c r="F306" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G306" s="12">
         <f>E306*F306*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H306" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28269,35 +28269,35 @@
       </c>
       <c r="L306" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M306" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N306" s="7">
         <f>L306*ROUNDUP(I306/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O306" s="7">
         <f>L306*(ROUNDUP(I306/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P306" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q306" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R306" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S306" s="13">
         <f>M306*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="307" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -28317,11 +28317,11 @@
         <v>2</v>
       </c>
       <c r="F307" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G307" s="12">
         <f>E307*F307*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>179.75999999999996</v>
+        <v>188.49599999999998</v>
       </c>
       <c r="H307" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28341,35 +28341,35 @@
       </c>
       <c r="L307" s="7">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M307" s="12">
         <f t="shared" si="26"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N307" s="7">
         <f>L307*ROUNDUP(I307/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O307" s="7">
         <f>L307*(ROUNDUP(I307/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P307" s="7">
         <f t="shared" si="27"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q307" s="7">
         <f t="shared" si="28"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R307" s="7">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S307" s="13">
         <f>M307*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="308" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -28389,11 +28389,11 @@
         <v>1</v>
       </c>
       <c r="F308" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G308" s="12">
         <f>E308*F308*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H308" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28413,35 +28413,35 @@
       </c>
       <c r="L308" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M308" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N308" s="7">
         <f>L308*ROUNDUP(I308/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O308" s="7">
         <f>L308*(ROUNDUP(I308/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P308" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q308" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R308" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S308" s="13">
         <f>M308*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="309" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -28461,11 +28461,11 @@
         <v>1</v>
       </c>
       <c r="F309" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G309" s="12">
         <f>E309*F309*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H309" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28485,35 +28485,35 @@
       </c>
       <c r="L309" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M309" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N309" s="7">
         <f>L309*ROUNDUP(I309/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O309" s="7">
         <f>L309*(ROUNDUP(I309/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P309" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q309" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R309" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S309" s="13">
         <f>M309*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="310" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -28533,11 +28533,11 @@
         <v>1</v>
       </c>
       <c r="F310" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G310" s="12">
         <f>E310*F310*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H310" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28557,35 +28557,35 @@
       </c>
       <c r="L310" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M310" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N310" s="7">
         <f>L310*ROUNDUP(I310/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O310" s="7">
         <f>L310*(ROUNDUP(I310/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P310" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q310" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R310" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S310" s="13">
         <f>M310*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="311" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -28605,11 +28605,11 @@
         <v>1</v>
       </c>
       <c r="F311" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G311" s="12">
         <f>E311*F311*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H311" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28629,35 +28629,35 @@
       </c>
       <c r="L311" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M311" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N311" s="7">
         <f>L311*ROUNDUP(I311/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O311" s="7">
         <f>L311*(ROUNDUP(I311/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P311" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q311" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R311" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S311" s="13">
         <f>M311*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="312" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -28677,11 +28677,11 @@
         <v>1</v>
       </c>
       <c r="F312" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G312" s="12">
         <f>E312*F312*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H312" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28701,35 +28701,35 @@
       </c>
       <c r="L312" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M312" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N312" s="7">
         <f>L312*ROUNDUP(I312/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O312" s="7">
         <f>L312*(ROUNDUP(I312/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P312" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q312" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R312" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S312" s="13">
         <f>M312*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="313" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -28749,11 +28749,11 @@
         <v>1</v>
       </c>
       <c r="F313" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G313" s="12">
         <f>E313*F313*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H313" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28773,35 +28773,35 @@
       </c>
       <c r="L313" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M313" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N313" s="7">
         <f>L313*ROUNDUP(I313/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O313" s="7">
         <f>L313*(ROUNDUP(I313/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P313" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q313" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R313" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S313" s="13">
         <f>M313*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="314" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -28821,11 +28821,11 @@
         <v>1</v>
       </c>
       <c r="F314" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G314" s="12">
         <f>E314*F314*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H314" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28845,35 +28845,35 @@
       </c>
       <c r="L314" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M314" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N314" s="7">
         <f>L314*ROUNDUP(I314/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O314" s="7">
         <f>L314*(ROUNDUP(I314/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P314" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q314" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R314" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S314" s="13">
         <f>M314*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="315" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -28893,11 +28893,11 @@
         <v>1</v>
       </c>
       <c r="F315" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G315" s="12">
         <f>E315*F315*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H315" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28917,35 +28917,35 @@
       </c>
       <c r="L315" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M315" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N315" s="7">
         <f>L315*ROUNDUP(I315/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O315" s="7">
         <f>L315*(ROUNDUP(I315/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P315" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q315" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R315" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S315" s="13">
         <f>M315*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="316" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -28965,11 +28965,11 @@
         <v>1</v>
       </c>
       <c r="F316" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G316" s="12">
         <f>E316*F316*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H316" s="7">
         <f>GiaDinh!$C$21</f>
@@ -28989,35 +28989,35 @@
       </c>
       <c r="L316" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M316" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N316" s="7">
         <f>L316*ROUNDUP(I316/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O316" s="7">
         <f>L316*(ROUNDUP(I316/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P316" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q316" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R316" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S316" s="13">
         <f>M316*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="317" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29037,11 +29037,11 @@
         <v>1</v>
       </c>
       <c r="F317" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G317" s="12">
         <f>E317*F317*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H317" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29061,35 +29061,35 @@
       </c>
       <c r="L317" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M317" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N317" s="7">
         <f>L317*ROUNDUP(I317/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O317" s="7">
         <f>L317*(ROUNDUP(I317/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P317" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q317" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R317" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S317" s="13">
         <f>M317*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="318" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29109,11 +29109,11 @@
         <v>1</v>
       </c>
       <c r="F318" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G318" s="12">
         <f>E318*F318*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H318" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29133,35 +29133,35 @@
       </c>
       <c r="L318" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M318" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N318" s="7">
         <f>L318*ROUNDUP(I318/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O318" s="7">
         <f>L318*(ROUNDUP(I318/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P318" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q318" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R318" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S318" s="13">
         <f>M318*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="319" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29181,11 +29181,11 @@
         <v>1</v>
       </c>
       <c r="F319" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G319" s="12">
         <f>E319*F319*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H319" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29205,35 +29205,35 @@
       </c>
       <c r="L319" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M319" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N319" s="7">
         <f>L319*ROUNDUP(I319/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O319" s="7">
         <f>L319*(ROUNDUP(I319/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P319" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q319" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R319" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S319" s="13">
         <f>M319*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="320" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29253,11 +29253,11 @@
         <v>1</v>
       </c>
       <c r="F320" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G320" s="12">
         <f>E320*F320*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H320" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29277,35 +29277,35 @@
       </c>
       <c r="L320" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M320" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N320" s="7">
         <f>L320*ROUNDUP(I320/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O320" s="7">
         <f>L320*(ROUNDUP(I320/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P320" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q320" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R320" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S320" s="13">
         <f>M320*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="321" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29325,11 +29325,11 @@
         <v>1</v>
       </c>
       <c r="F321" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G321" s="12">
         <f>E321*F321*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H321" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29349,35 +29349,35 @@
       </c>
       <c r="L321" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M321" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N321" s="7">
         <f>L321*ROUNDUP(I321/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O321" s="7">
         <f>L321*(ROUNDUP(I321/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P321" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q321" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R321" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S321" s="13">
         <f>M321*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="322" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29397,11 +29397,11 @@
         <v>1</v>
       </c>
       <c r="F322" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G322" s="12">
         <f>E322*F322*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H322" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29421,35 +29421,35 @@
       </c>
       <c r="L322" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M322" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N322" s="7">
         <f>L322*ROUNDUP(I322/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O322" s="7">
         <f>L322*(ROUNDUP(I322/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P322" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q322" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R322" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S322" s="13">
         <f>M322*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="323" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29469,11 +29469,11 @@
         <v>1</v>
       </c>
       <c r="F323" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G323" s="12">
         <f>E323*F323*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H323" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29493,35 +29493,35 @@
       </c>
       <c r="L323" s="7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M323" s="12">
         <f t="shared" si="26"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N323" s="7">
         <f>L323*ROUNDUP(I323/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O323" s="7">
         <f>L323*(ROUNDUP(I323/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P323" s="7">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q323" s="7">
         <f t="shared" si="28"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R323" s="7">
         <f t="shared" si="29"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S323" s="13">
         <f>M323*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="324" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29541,11 +29541,11 @@
         <v>1</v>
       </c>
       <c r="F324" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G324" s="12">
         <f>E324*F324*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H324" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29565,35 +29565,35 @@
       </c>
       <c r="L324" s="7">
         <f t="shared" ref="L324:L387" si="31">MAX(1,ROUNDUP(G324/K324-0.0005,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M324" s="12">
         <f t="shared" ref="M324:M387" si="32">L324*I324</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N324" s="7">
         <f>L324*ROUNDUP(I324/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O324" s="7">
         <f>L324*(ROUNDUP(I324/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P324" s="7">
         <f t="shared" ref="P324:P375" si="33">L324*J324</f>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q324" s="7">
         <f t="shared" ref="Q324:Q387" si="34">2*P324</f>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R324" s="7">
         <f t="shared" ref="R324:R375" si="35">P324</f>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S324" s="13">
         <f>M324*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="325" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29613,11 +29613,11 @@
         <v>1</v>
       </c>
       <c r="F325" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G325" s="12">
         <f>E325*F325*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H325" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29637,35 +29637,35 @@
       </c>
       <c r="L325" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M325" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N325" s="7">
         <f>L325*ROUNDUP(I325/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O325" s="7">
         <f>L325*(ROUNDUP(I325/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P325" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q325" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R325" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S325" s="13">
         <f>M325*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="326" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29685,11 +29685,11 @@
         <v>1</v>
       </c>
       <c r="F326" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G326" s="12">
         <f>E326*F326*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H326" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29709,35 +29709,35 @@
       </c>
       <c r="L326" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M326" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N326" s="7">
         <f>L326*ROUNDUP(I326/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O326" s="7">
         <f>L326*(ROUNDUP(I326/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P326" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q326" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R326" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S326" s="13">
         <f>M326*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="327" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -29757,11 +29757,11 @@
         <v>1</v>
       </c>
       <c r="F327" s="7">
-        <v>107</v>
+        <v>112.2</v>
       </c>
       <c r="G327" s="12">
         <f>E327*F327*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>89.879999999999981</v>
+        <v>94.24799999999999</v>
       </c>
       <c r="H327" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29781,35 +29781,35 @@
       </c>
       <c r="L327" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M327" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N327" s="7">
         <f>L327*ROUNDUP(I327/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O327" s="7">
         <f>L327*(ROUNDUP(I327/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P327" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q327" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R327" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S327" s="13">
         <f>M327*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="328" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -29829,11 +29829,11 @@
         <v>2</v>
       </c>
       <c r="F328" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G328" s="12">
         <f>E328*F328*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H328" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29853,35 +29853,35 @@
       </c>
       <c r="L328" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M328" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N328" s="7">
         <f>L328*ROUNDUP(I328/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O328" s="7">
         <f>L328*(ROUNDUP(I328/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P328" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q328" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R328" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S328" s="13">
         <f>M328*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="329" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -29901,11 +29901,11 @@
         <v>2</v>
       </c>
       <c r="F329" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G329" s="12">
         <f>E329*F329*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H329" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29925,35 +29925,35 @@
       </c>
       <c r="L329" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M329" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N329" s="7">
         <f>L329*ROUNDUP(I329/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O329" s="7">
         <f>L329*(ROUNDUP(I329/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P329" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q329" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R329" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S329" s="13">
         <f>M329*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="330" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -29973,11 +29973,11 @@
         <v>2</v>
       </c>
       <c r="F330" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G330" s="12">
         <f>E330*F330*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H330" s="7">
         <f>GiaDinh!$C$21</f>
@@ -29997,35 +29997,35 @@
       </c>
       <c r="L330" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M330" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N330" s="7">
         <f>L330*ROUNDUP(I330/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O330" s="7">
         <f>L330*(ROUNDUP(I330/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P330" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q330" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R330" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S330" s="13">
         <f>M330*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="331" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30045,11 +30045,11 @@
         <v>2</v>
       </c>
       <c r="F331" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G331" s="12">
         <f>E331*F331*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H331" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30069,35 +30069,35 @@
       </c>
       <c r="L331" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M331" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N331" s="7">
         <f>L331*ROUNDUP(I331/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O331" s="7">
         <f>L331*(ROUNDUP(I331/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P331" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q331" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R331" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S331" s="13">
         <f>M331*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="332" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30117,11 +30117,11 @@
         <v>2</v>
       </c>
       <c r="F332" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G332" s="12">
         <f>E332*F332*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H332" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30141,35 +30141,35 @@
       </c>
       <c r="L332" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M332" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N332" s="7">
         <f>L332*ROUNDUP(I332/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O332" s="7">
         <f>L332*(ROUNDUP(I332/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P332" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q332" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R332" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S332" s="13">
         <f>M332*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="333" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30189,11 +30189,11 @@
         <v>2</v>
       </c>
       <c r="F333" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G333" s="12">
         <f>E333*F333*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H333" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30213,35 +30213,35 @@
       </c>
       <c r="L333" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M333" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N333" s="7">
         <f>L333*ROUNDUP(I333/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O333" s="7">
         <f>L333*(ROUNDUP(I333/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P333" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q333" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R333" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S333" s="13">
         <f>M333*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="334" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30261,11 +30261,11 @@
         <v>2</v>
       </c>
       <c r="F334" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G334" s="12">
         <f>E334*F334*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H334" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30285,35 +30285,35 @@
       </c>
       <c r="L334" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M334" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N334" s="7">
         <f>L334*ROUNDUP(I334/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O334" s="7">
         <f>L334*(ROUNDUP(I334/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P334" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q334" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R334" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S334" s="13">
         <f>M334*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="335" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30333,11 +30333,11 @@
         <v>2</v>
       </c>
       <c r="F335" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G335" s="12">
         <f>E335*F335*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H335" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30357,35 +30357,35 @@
       </c>
       <c r="L335" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M335" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N335" s="7">
         <f>L335*ROUNDUP(I335/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O335" s="7">
         <f>L335*(ROUNDUP(I335/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P335" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q335" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R335" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S335" s="13">
         <f>M335*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="336" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30405,11 +30405,11 @@
         <v>2</v>
       </c>
       <c r="F336" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G336" s="12">
         <f>E336*F336*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H336" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30429,35 +30429,35 @@
       </c>
       <c r="L336" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M336" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N336" s="7">
         <f>L336*ROUNDUP(I336/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O336" s="7">
         <f>L336*(ROUNDUP(I336/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P336" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q336" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R336" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S336" s="13">
         <f>M336*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="337" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30477,11 +30477,11 @@
         <v>2</v>
       </c>
       <c r="F337" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G337" s="12">
         <f>E337*F337*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H337" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30501,35 +30501,35 @@
       </c>
       <c r="L337" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M337" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N337" s="7">
         <f>L337*ROUNDUP(I337/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O337" s="7">
         <f>L337*(ROUNDUP(I337/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P337" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q337" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R337" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S337" s="13">
         <f>M337*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="338" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30549,11 +30549,11 @@
         <v>2</v>
       </c>
       <c r="F338" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G338" s="12">
         <f>E338*F338*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H338" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30573,35 +30573,35 @@
       </c>
       <c r="L338" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M338" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N338" s="7">
         <f>L338*ROUNDUP(I338/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O338" s="7">
         <f>L338*(ROUNDUP(I338/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P338" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q338" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R338" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S338" s="13">
         <f>M338*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="339" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30621,11 +30621,11 @@
         <v>2</v>
       </c>
       <c r="F339" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G339" s="12">
         <f>E339*F339*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H339" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30645,35 +30645,35 @@
       </c>
       <c r="L339" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M339" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N339" s="7">
         <f>L339*ROUNDUP(I339/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O339" s="7">
         <f>L339*(ROUNDUP(I339/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P339" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q339" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R339" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S339" s="13">
         <f>M339*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="340" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30693,11 +30693,11 @@
         <v>2</v>
       </c>
       <c r="F340" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G340" s="12">
         <f>E340*F340*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H340" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30717,35 +30717,35 @@
       </c>
       <c r="L340" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M340" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N340" s="7">
         <f>L340*ROUNDUP(I340/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O340" s="7">
         <f>L340*(ROUNDUP(I340/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P340" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q340" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R340" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S340" s="13">
         <f>M340*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="341" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30765,11 +30765,11 @@
         <v>2</v>
       </c>
       <c r="F341" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G341" s="12">
         <f>E341*F341*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H341" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30789,35 +30789,35 @@
       </c>
       <c r="L341" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M341" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N341" s="7">
         <f>L341*ROUNDUP(I341/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O341" s="7">
         <f>L341*(ROUNDUP(I341/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P341" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q341" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R341" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S341" s="13">
         <f>M341*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="342" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30837,11 +30837,11 @@
         <v>2</v>
       </c>
       <c r="F342" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G342" s="12">
         <f>E342*F342*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H342" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30861,35 +30861,35 @@
       </c>
       <c r="L342" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M342" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N342" s="7">
         <f>L342*ROUNDUP(I342/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O342" s="7">
         <f>L342*(ROUNDUP(I342/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P342" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q342" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R342" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S342" s="13">
         <f>M342*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="343" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30909,11 +30909,11 @@
         <v>2</v>
       </c>
       <c r="F343" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G343" s="12">
         <f>E343*F343*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H343" s="7">
         <f>GiaDinh!$C$21</f>
@@ -30933,35 +30933,35 @@
       </c>
       <c r="L343" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M343" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N343" s="7">
         <f>L343*ROUNDUP(I343/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O343" s="7">
         <f>L343*(ROUNDUP(I343/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P343" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q343" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R343" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S343" s="13">
         <f>M343*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="344" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -30981,11 +30981,11 @@
         <v>2</v>
       </c>
       <c r="F344" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G344" s="12">
         <f>E344*F344*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H344" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31005,35 +31005,35 @@
       </c>
       <c r="L344" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M344" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N344" s="7">
         <f>L344*ROUNDUP(I344/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O344" s="7">
         <f>L344*(ROUNDUP(I344/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P344" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q344" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R344" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S344" s="13">
         <f>M344*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="345" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -31053,11 +31053,11 @@
         <v>2</v>
       </c>
       <c r="F345" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G345" s="12">
         <f>E345*F345*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>157.91999999999999</v>
+        <v>197.23199999999997</v>
       </c>
       <c r="H345" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31077,35 +31077,35 @@
       </c>
       <c r="L345" s="7">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M345" s="12">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N345" s="7">
         <f>L345*ROUNDUP(I345/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O345" s="7">
         <f>L345*(ROUNDUP(I345/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P345" s="7">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q345" s="7">
         <f t="shared" si="34"/>
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="R345" s="7">
         <f t="shared" si="35"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S345" s="13">
         <f>M345*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="346" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31125,11 +31125,11 @@
         <v>1</v>
       </c>
       <c r="F346" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G346" s="12">
         <f>E346*F346*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H346" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31149,35 +31149,35 @@
       </c>
       <c r="L346" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M346" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N346" s="7">
         <f>L346*ROUNDUP(I346/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O346" s="7">
         <f>L346*(ROUNDUP(I346/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P346" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q346" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R346" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S346" s="13">
         <f>M346*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="347" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31197,11 +31197,11 @@
         <v>1</v>
       </c>
       <c r="F347" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G347" s="12">
         <f>E347*F347*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H347" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31221,35 +31221,35 @@
       </c>
       <c r="L347" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M347" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N347" s="7">
         <f>L347*ROUNDUP(I347/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O347" s="7">
         <f>L347*(ROUNDUP(I347/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P347" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q347" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R347" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S347" s="13">
         <f>M347*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="348" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31269,11 +31269,11 @@
         <v>1</v>
       </c>
       <c r="F348" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G348" s="12">
         <f>E348*F348*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H348" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31293,35 +31293,35 @@
       </c>
       <c r="L348" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M348" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N348" s="7">
         <f>L348*ROUNDUP(I348/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O348" s="7">
         <f>L348*(ROUNDUP(I348/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P348" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q348" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R348" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S348" s="13">
         <f>M348*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="349" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31341,11 +31341,11 @@
         <v>1</v>
       </c>
       <c r="F349" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G349" s="12">
         <f>E349*F349*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H349" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31365,35 +31365,35 @@
       </c>
       <c r="L349" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M349" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N349" s="7">
         <f>L349*ROUNDUP(I349/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O349" s="7">
         <f>L349*(ROUNDUP(I349/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P349" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q349" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R349" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S349" s="13">
         <f>M349*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="350" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31413,11 +31413,11 @@
         <v>1</v>
       </c>
       <c r="F350" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G350" s="12">
         <f>E350*F350*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H350" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31437,35 +31437,35 @@
       </c>
       <c r="L350" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M350" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N350" s="7">
         <f>L350*ROUNDUP(I350/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O350" s="7">
         <f>L350*(ROUNDUP(I350/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P350" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q350" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R350" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S350" s="13">
         <f>M350*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="351" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31485,11 +31485,11 @@
         <v>1</v>
       </c>
       <c r="F351" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G351" s="12">
         <f>E351*F351*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H351" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31509,35 +31509,35 @@
       </c>
       <c r="L351" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M351" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N351" s="7">
         <f>L351*ROUNDUP(I351/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O351" s="7">
         <f>L351*(ROUNDUP(I351/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P351" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q351" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R351" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S351" s="13">
         <f>M351*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="352" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31557,11 +31557,11 @@
         <v>1</v>
       </c>
       <c r="F352" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G352" s="12">
         <f>E352*F352*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H352" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31581,35 +31581,35 @@
       </c>
       <c r="L352" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M352" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N352" s="7">
         <f>L352*ROUNDUP(I352/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O352" s="7">
         <f>L352*(ROUNDUP(I352/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P352" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q352" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R352" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S352" s="13">
         <f>M352*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="353" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31629,11 +31629,11 @@
         <v>1</v>
       </c>
       <c r="F353" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G353" s="12">
         <f>E353*F353*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H353" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31653,35 +31653,35 @@
       </c>
       <c r="L353" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M353" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N353" s="7">
         <f>L353*ROUNDUP(I353/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O353" s="7">
         <f>L353*(ROUNDUP(I353/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P353" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q353" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R353" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S353" s="13">
         <f>M353*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="354" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31701,11 +31701,11 @@
         <v>1</v>
       </c>
       <c r="F354" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G354" s="12">
         <f>E354*F354*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H354" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31725,35 +31725,35 @@
       </c>
       <c r="L354" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M354" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N354" s="7">
         <f>L354*ROUNDUP(I354/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O354" s="7">
         <f>L354*(ROUNDUP(I354/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P354" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q354" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R354" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S354" s="13">
         <f>M354*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="355" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31773,11 +31773,11 @@
         <v>1</v>
       </c>
       <c r="F355" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G355" s="12">
         <f>E355*F355*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H355" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31797,35 +31797,35 @@
       </c>
       <c r="L355" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M355" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N355" s="7">
         <f>L355*ROUNDUP(I355/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O355" s="7">
         <f>L355*(ROUNDUP(I355/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P355" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q355" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R355" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S355" s="13">
         <f>M355*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="356" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31845,11 +31845,11 @@
         <v>1</v>
       </c>
       <c r="F356" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G356" s="12">
         <f>E356*F356*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H356" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31869,35 +31869,35 @@
       </c>
       <c r="L356" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M356" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N356" s="7">
         <f>L356*ROUNDUP(I356/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O356" s="7">
         <f>L356*(ROUNDUP(I356/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P356" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q356" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R356" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S356" s="13">
         <f>M356*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="357" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31917,11 +31917,11 @@
         <v>1</v>
       </c>
       <c r="F357" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G357" s="12">
         <f>E357*F357*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H357" s="7">
         <f>GiaDinh!$C$21</f>
@@ -31941,35 +31941,35 @@
       </c>
       <c r="L357" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M357" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N357" s="7">
         <f>L357*ROUNDUP(I357/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O357" s="7">
         <f>L357*(ROUNDUP(I357/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P357" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q357" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R357" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S357" s="13">
         <f>M357*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="358" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -31989,11 +31989,11 @@
         <v>1</v>
       </c>
       <c r="F358" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G358" s="12">
         <f>E358*F358*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H358" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32013,35 +32013,35 @@
       </c>
       <c r="L358" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M358" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N358" s="7">
         <f>L358*ROUNDUP(I358/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O358" s="7">
         <f>L358*(ROUNDUP(I358/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P358" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q358" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R358" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S358" s="13">
         <f>M358*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="359" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32061,11 +32061,11 @@
         <v>1</v>
       </c>
       <c r="F359" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G359" s="12">
         <f>E359*F359*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H359" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32085,35 +32085,35 @@
       </c>
       <c r="L359" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M359" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N359" s="7">
         <f>L359*ROUNDUP(I359/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O359" s="7">
         <f>L359*(ROUNDUP(I359/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P359" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q359" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R359" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S359" s="13">
         <f>M359*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="360" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32133,11 +32133,11 @@
         <v>1</v>
       </c>
       <c r="F360" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G360" s="12">
         <f>E360*F360*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H360" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32157,35 +32157,35 @@
       </c>
       <c r="L360" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M360" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N360" s="7">
         <f>L360*ROUNDUP(I360/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O360" s="7">
         <f>L360*(ROUNDUP(I360/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P360" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q360" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R360" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S360" s="13">
         <f>M360*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="361" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32205,11 +32205,11 @@
         <v>1</v>
       </c>
       <c r="F361" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G361" s="12">
         <f>E361*F361*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H361" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32229,35 +32229,35 @@
       </c>
       <c r="L361" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M361" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N361" s="7">
         <f>L361*ROUNDUP(I361/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O361" s="7">
         <f>L361*(ROUNDUP(I361/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P361" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q361" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R361" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S361" s="13">
         <f>M361*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="362" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32277,11 +32277,11 @@
         <v>1</v>
       </c>
       <c r="F362" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G362" s="12">
         <f>E362*F362*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H362" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32301,35 +32301,35 @@
       </c>
       <c r="L362" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M362" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N362" s="7">
         <f>L362*ROUNDUP(I362/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O362" s="7">
         <f>L362*(ROUNDUP(I362/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P362" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q362" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R362" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S362" s="13">
         <f>M362*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="363" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32349,11 +32349,11 @@
         <v>1</v>
       </c>
       <c r="F363" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G363" s="12">
         <f>E363*F363*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H363" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32373,35 +32373,35 @@
       </c>
       <c r="L363" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M363" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N363" s="7">
         <f>L363*ROUNDUP(I363/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O363" s="7">
         <f>L363*(ROUNDUP(I363/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P363" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q363" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R363" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S363" s="13">
         <f>M363*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="364" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32421,11 +32421,11 @@
         <v>1</v>
       </c>
       <c r="F364" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G364" s="12">
         <f>E364*F364*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H364" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32445,35 +32445,35 @@
       </c>
       <c r="L364" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M364" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N364" s="7">
         <f>L364*ROUNDUP(I364/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O364" s="7">
         <f>L364*(ROUNDUP(I364/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P364" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q364" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R364" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S364" s="13">
         <f>M364*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="365" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32493,11 +32493,11 @@
         <v>1</v>
       </c>
       <c r="F365" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G365" s="12">
         <f>E365*F365*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H365" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32517,35 +32517,35 @@
       </c>
       <c r="L365" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M365" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N365" s="7">
         <f>L365*ROUNDUP(I365/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O365" s="7">
         <f>L365*(ROUNDUP(I365/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P365" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q365" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R365" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S365" s="13">
         <f>M365*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="366" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32565,11 +32565,11 @@
         <v>1</v>
       </c>
       <c r="F366" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G366" s="12">
         <f>E366*F366*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H366" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32589,35 +32589,35 @@
       </c>
       <c r="L366" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M366" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N366" s="7">
         <f>L366*ROUNDUP(I366/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O366" s="7">
         <f>L366*(ROUNDUP(I366/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P366" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q366" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R366" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S366" s="13">
         <f>M366*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="367" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32637,11 +32637,11 @@
         <v>1</v>
       </c>
       <c r="F367" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G367" s="12">
         <f>E367*F367*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H367" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32661,35 +32661,35 @@
       </c>
       <c r="L367" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M367" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N367" s="7">
         <f>L367*ROUNDUP(I367/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O367" s="7">
         <f>L367*(ROUNDUP(I367/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P367" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q367" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R367" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S367" s="13">
         <f>M367*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="368" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32709,11 +32709,11 @@
         <v>1</v>
       </c>
       <c r="F368" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G368" s="12">
         <f>E368*F368*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H368" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32733,35 +32733,35 @@
       </c>
       <c r="L368" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M368" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N368" s="7">
         <f>L368*ROUNDUP(I368/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O368" s="7">
         <f>L368*(ROUNDUP(I368/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P368" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q368" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R368" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S368" s="13">
         <f>M368*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="369" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32781,11 +32781,11 @@
         <v>1</v>
       </c>
       <c r="F369" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G369" s="12">
         <f>E369*F369*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H369" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32805,35 +32805,35 @@
       </c>
       <c r="L369" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M369" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N369" s="7">
         <f>L369*ROUNDUP(I369/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O369" s="7">
         <f>L369*(ROUNDUP(I369/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P369" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q369" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R369" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S369" s="13">
         <f>M369*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="370" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32853,11 +32853,11 @@
         <v>1</v>
       </c>
       <c r="F370" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G370" s="12">
         <f>E370*F370*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H370" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32877,35 +32877,35 @@
       </c>
       <c r="L370" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M370" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N370" s="7">
         <f>L370*ROUNDUP(I370/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O370" s="7">
         <f>L370*(ROUNDUP(I370/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P370" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q370" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R370" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S370" s="13">
         <f>M370*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="371" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32925,11 +32925,11 @@
         <v>1</v>
       </c>
       <c r="F371" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G371" s="12">
         <f>E371*F371*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H371" s="7">
         <f>GiaDinh!$C$21</f>
@@ -32949,35 +32949,35 @@
       </c>
       <c r="L371" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M371" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N371" s="7">
         <f>L371*ROUNDUP(I371/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O371" s="7">
         <f>L371*(ROUNDUP(I371/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P371" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q371" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R371" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S371" s="13">
         <f>M371*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="372" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -32997,11 +32997,11 @@
         <v>1</v>
       </c>
       <c r="F372" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G372" s="12">
         <f>E372*F372*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H372" s="7">
         <f>GiaDinh!$C$21</f>
@@ -33021,35 +33021,35 @@
       </c>
       <c r="L372" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M372" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N372" s="7">
         <f>L372*ROUNDUP(I372/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O372" s="7">
         <f>L372*(ROUNDUP(I372/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P372" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q372" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R372" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S372" s="13">
         <f>M372*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="373" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -33069,11 +33069,11 @@
         <v>1</v>
       </c>
       <c r="F373" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G373" s="12">
         <f>E373*F373*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H373" s="7">
         <f>GiaDinh!$C$21</f>
@@ -33093,35 +33093,35 @@
       </c>
       <c r="L373" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M373" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N373" s="7">
         <f>L373*ROUNDUP(I373/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O373" s="7">
         <f>L373*(ROUNDUP(I373/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P373" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q373" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R373" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S373" s="13">
         <f>M373*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="374" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -33141,11 +33141,11 @@
         <v>1</v>
       </c>
       <c r="F374" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G374" s="12">
         <f>E374*F374*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H374" s="7">
         <f>GiaDinh!$C$21</f>
@@ -33165,35 +33165,35 @@
       </c>
       <c r="L374" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M374" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N374" s="7">
         <f>L374*ROUNDUP(I374/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O374" s="7">
         <f>L374*(ROUNDUP(I374/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P374" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q374" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R374" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S374" s="13">
         <f>M374*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="375" spans="1:19" ht="46.5" x14ac:dyDescent="0.35">
@@ -33213,11 +33213,11 @@
         <v>1</v>
       </c>
       <c r="F375" s="7">
-        <v>94</v>
+        <v>117.4</v>
       </c>
       <c r="G375" s="12">
         <f>E375*F375*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>78.959999999999994</v>
+        <v>98.615999999999985</v>
       </c>
       <c r="H375" s="7">
         <f>GiaDinh!$C$21</f>
@@ -33237,35 +33237,35 @@
       </c>
       <c r="L375" s="7">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M375" s="12">
         <f t="shared" si="32"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N375" s="7">
         <f>L375*ROUNDUP(I375/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O375" s="7">
         <f>L375*(ROUNDUP(I375/GiaDinh!$C$5-0.0005,0)-1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P375" s="7">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q375" s="7">
         <f t="shared" si="34"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="R375" s="7">
         <f t="shared" si="35"/>
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S375" s="13">
         <f>M375*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>90.3</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_BE_PIN.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_BE_PIN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nhatm\AppData\Local\Temp\claude\E--Out-Job-Chu-Giap-Web-t-nh-neo-b-\6aeb2207-6b11-48a0-9210-732f1cccfe43\scratchpad\bmkc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2527E6F4-7FD8-4C3D-A1E0-8BB7AA031DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D5EDF0A-BABD-46BE-8738-101EE301844E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="2890" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14937,11 +14937,11 @@
         <v>2</v>
       </c>
       <c r="F124" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G124" s="11">
         <f>2*F124*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>128.51999999999998</v>
+        <v>132.21599999999998</v>
       </c>
       <c r="H124" s="7">
         <v>12</v>
@@ -15005,11 +15005,11 @@
         <v>2</v>
       </c>
       <c r="F125" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G125" s="11">
         <f>2*F125*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>128.51999999999998</v>
+        <v>132.21599999999998</v>
       </c>
       <c r="H125" s="7">
         <v>12</v>
@@ -15073,11 +15073,11 @@
         <v>2</v>
       </c>
       <c r="F126" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G126" s="11">
         <f>2*F126*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>128.51999999999998</v>
+        <v>132.21599999999998</v>
       </c>
       <c r="H126" s="7">
         <v>13</v>
@@ -15141,11 +15141,11 @@
         <v>2</v>
       </c>
       <c r="F127" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G127" s="11">
         <f>2*F127*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>128.51999999999998</v>
+        <v>132.21599999999998</v>
       </c>
       <c r="H127" s="7">
         <v>12</v>
@@ -15209,11 +15209,11 @@
         <v>4</v>
       </c>
       <c r="F128" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G128" s="11">
         <f>4*F128*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>257.03999999999996</v>
+        <v>264.43199999999996</v>
       </c>
       <c r="H128" s="7">
         <v>11</v>
@@ -15277,11 +15277,11 @@
         <v>2</v>
       </c>
       <c r="F129" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G129" s="11">
         <f>2*F129*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>128.51999999999998</v>
+        <v>132.21599999999998</v>
       </c>
       <c r="H129" s="7">
         <v>13</v>
@@ -15345,11 +15345,11 @@
         <v>1</v>
       </c>
       <c r="F130" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G130" s="11">
         <f>1*F130*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H130" s="7">
         <v>13</v>
@@ -15413,11 +15413,11 @@
         <v>1</v>
       </c>
       <c r="F131" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G131" s="11">
         <f>1*F131*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H131" s="7">
         <v>13</v>
@@ -15481,11 +15481,11 @@
         <v>1</v>
       </c>
       <c r="F132" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G132" s="11">
         <f>1*F132*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H132" s="7">
         <v>13</v>
@@ -15549,11 +15549,11 @@
         <v>1</v>
       </c>
       <c r="F133" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G133" s="11">
         <f>1*F133*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H133" s="7">
         <v>13</v>
@@ -15617,11 +15617,11 @@
         <v>1</v>
       </c>
       <c r="F134" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G134" s="11">
         <f>1*F134*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H134" s="7">
         <v>13</v>
@@ -15685,11 +15685,11 @@
         <v>1</v>
       </c>
       <c r="F135" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G135" s="11">
         <f>1*F135*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H135" s="7">
         <v>13</v>
@@ -15753,11 +15753,11 @@
         <v>1</v>
       </c>
       <c r="F136" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G136" s="11">
         <f>1*F136*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H136" s="7">
         <v>13</v>
@@ -15821,11 +15821,11 @@
         <v>1</v>
       </c>
       <c r="F137" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G137" s="11">
         <f>1*F137*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H137" s="7">
         <v>13</v>
@@ -15889,11 +15889,11 @@
         <v>1</v>
       </c>
       <c r="F138" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G138" s="11">
         <f>1*F138*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H138" s="7">
         <v>13</v>
@@ -15957,11 +15957,11 @@
         <v>1</v>
       </c>
       <c r="F139" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G139" s="11">
         <f>1*F139*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H139" s="7">
         <v>13</v>
@@ -16025,11 +16025,11 @@
         <v>1</v>
       </c>
       <c r="F140" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G140" s="11">
         <f>1*F140*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H140" s="7">
         <v>12</v>
@@ -16093,11 +16093,11 @@
         <v>1</v>
       </c>
       <c r="F141" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G141" s="11">
         <f>1*F141*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H141" s="7">
         <v>12</v>
@@ -16161,11 +16161,11 @@
         <v>1</v>
       </c>
       <c r="F142" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G142" s="11">
         <f>1*F142*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H142" s="7">
         <v>12</v>
@@ -16229,11 +16229,11 @@
         <v>1</v>
       </c>
       <c r="F143" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G143" s="11">
         <f>1*F143*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H143" s="7">
         <v>12</v>
@@ -16297,11 +16297,11 @@
         <v>1</v>
       </c>
       <c r="F144" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G144" s="11">
         <f>1*F144*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H144" s="7">
         <v>12</v>
@@ -16365,11 +16365,11 @@
         <v>1</v>
       </c>
       <c r="F145" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G145" s="11">
         <f>1*F145*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H145" s="7">
         <v>12</v>
@@ -16433,11 +16433,11 @@
         <v>1</v>
       </c>
       <c r="F146" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G146" s="11">
         <f>1*F146*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H146" s="7">
         <v>12</v>
@@ -16501,11 +16501,11 @@
         <v>1</v>
       </c>
       <c r="F147" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G147" s="11">
         <f>1*F147*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H147" s="7">
         <v>12</v>
@@ -16569,11 +16569,11 @@
         <v>1</v>
       </c>
       <c r="F148" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G148" s="11">
         <f>1*F148*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H148" s="7">
         <v>12</v>
@@ -16637,11 +16637,11 @@
         <v>1</v>
       </c>
       <c r="F149" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G149" s="11">
         <f>1*F149*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H149" s="7">
         <v>12</v>
@@ -16705,11 +16705,11 @@
         <v>1</v>
       </c>
       <c r="F150" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G150" s="11">
         <f>1*F150*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H150" s="7">
         <v>12</v>
@@ -16773,11 +16773,11 @@
         <v>1</v>
       </c>
       <c r="F151" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G151" s="11">
         <f>1*F151*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H151" s="7">
         <v>12</v>
@@ -16841,11 +16841,11 @@
         <v>1</v>
       </c>
       <c r="F152" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G152" s="11">
         <f>1*F152*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H152" s="7">
         <v>12</v>
@@ -16909,11 +16909,11 @@
         <v>1</v>
       </c>
       <c r="F153" s="7">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="G153" s="11">
         <f>1*F153*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>64.259999999999991</v>
+        <v>66.10799999999999</v>
       </c>
       <c r="H153" s="7">
         <v>12</v>

--- a/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_BE_PIN.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_BE_PIN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nhatm\AppData\Local\Temp\claude\E--Out-Job-Chu-Giap-Web-t-nh-neo-b-\6aeb2207-6b11-48a0-9210-732f1cccfe43\scratchpad\bmkc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D5EDF0A-BABD-46BE-8738-101EE301844E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9879681-D547-425A-97F0-4814D1BC3D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="2890" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,7 +303,7 @@
     <t>NEO</t>
   </si>
   <si>
-    <t>Cáp 2 nhánh chữ Y: 2 bích mỗi dây, bắt vào hộp 40x60 gia cường; mắt nhánh cáp móc thẳng vào ma ní này. Số dây theo mặt bằng neo của web (215 dây); dây nối hai bè: 1 bích mỗi đầu (14 dây nối)</t>
+    <t>Cáp 2 nhánh chữ Y: 2 bích mỗi dây, bắt vào hộp 40x60 gia cường; mắt nhánh cáp móc thẳng vào ma ní này. Số dây theo mặt bằng neo của web (211 dây); dây nối hai bè: 1 bích mỗi đầu (18 dây nối)</t>
   </si>
   <si>
     <t>SỐ LIỆU LẤY TỪ BẢN VẼ "BO TRI BE PIN HO BAN MONG" (bảng Revit trên các tờ CT-BP-01…06, MB-B01-01) VÀ BẢN VẼ CAD KHUNG "CT-KC-BE-01…06" (30/10/2026)</t>
@@ -1032,211 +1032,211 @@
     <t>B2-15</t>
   </si>
   <si>
-    <t>B2-D56a, B2-D58a, B2-D56b, B2-D58b, B2-D24a</t>
+    <t>B2-D56a, B2-D56b, T23-02, T23-03, T23-01</t>
   </si>
   <si>
     <t>B2-16</t>
   </si>
   <si>
-    <t>B2-D24b</t>
+    <t>B2-D11a, B2-D11b</t>
   </si>
   <si>
     <t>B2-17</t>
   </si>
   <si>
-    <t>B2-D11a, B2-D11b</t>
+    <t>B2-D38b, B2-D38a, B2-D14b</t>
   </si>
   <si>
     <t>B2-18</t>
   </si>
   <si>
-    <t>B2-D38b, B2-D38a, B2-D14b</t>
+    <t>B2-D14a</t>
   </si>
   <si>
     <t>B2-19</t>
   </si>
   <si>
-    <t>B2-D14a</t>
+    <t>B2-D26b, B2-D26a, B2-D41b</t>
   </si>
   <si>
     <t>B2-20</t>
   </si>
   <si>
-    <t>B2-D26b, B2-D26a, B2-D41b</t>
+    <t>B2-D41a, B2-D06b, B2-D06a</t>
   </si>
   <si>
     <t>B2-21</t>
   </si>
   <si>
-    <t>B2-D41a, B2-D06b, B2-D06a</t>
+    <t>B2-D19b, B2-D19a, B2-D52b</t>
   </si>
   <si>
     <t>B2-22</t>
   </si>
   <si>
-    <t>B2-D19b, B2-D19a, B2-D52b</t>
+    <t>B2-D52a, B2-D13b, B2-D13a</t>
   </si>
   <si>
     <t>B2-23</t>
   </si>
   <si>
-    <t>B2-D52a, B2-D13b, B2-D13a</t>
+    <t>B2-D55b, B2-D55a, B2-D48b, B2-D48a</t>
   </si>
   <si>
     <t>B2-24</t>
   </si>
   <si>
-    <t>B2-D55b, B2-D55a, B2-D48b, B2-D48a</t>
+    <t>B2-D29b, B2-D29a</t>
   </si>
   <si>
     <t>B2-25</t>
   </si>
   <si>
-    <t>B2-D29b, B2-D29a</t>
+    <t>B2-D04b, B2-D04a, B2-D36b</t>
   </si>
   <si>
     <t>B2-26</t>
   </si>
   <si>
-    <t>B2-D04b, B2-D04a, B2-D36b</t>
+    <t>B2-D36a, B2-D31b, B2-D31a</t>
   </si>
   <si>
     <t>B2-27</t>
   </si>
   <si>
-    <t>B2-D36a, B2-D31b, B2-D31a</t>
+    <t>B2-D15b, B2-D15a, B2-D43b</t>
   </si>
   <si>
     <t>B2-28</t>
   </si>
   <si>
-    <t>B2-D15b, B2-D15a, B2-D43b</t>
+    <t>B2-D43a, B2-D20b, B2-D20a</t>
   </si>
   <si>
     <t>B2-29</t>
   </si>
   <si>
-    <t>B2-D43a, B2-D20b, B2-D20a</t>
+    <t>B2-D51b, B2-D51a, B2-D07b</t>
   </si>
   <si>
     <t>B2-30</t>
   </si>
   <si>
-    <t>B2-D51b, B2-D51a, B2-D07b</t>
+    <t>B2-D07a, B2-D53b, B2-D53a</t>
   </si>
   <si>
     <t>B2-31</t>
   </si>
   <si>
-    <t>B2-D07a, B2-D53b, B2-D53a</t>
+    <t>B2-D37b</t>
   </si>
   <si>
     <t>B2-32</t>
   </si>
   <si>
-    <t>B2-D37b</t>
+    <t>B2-D37a</t>
   </si>
   <si>
     <t>B2-33</t>
   </si>
   <si>
-    <t>B2-D37a</t>
+    <t>B2-D12b</t>
   </si>
   <si>
     <t>B2-34</t>
   </si>
   <si>
-    <t>B2-D12b</t>
+    <t>B2-D12a</t>
   </si>
   <si>
     <t>B2-35</t>
   </si>
   <si>
-    <t>B2-D12a</t>
+    <t>B2-D27b</t>
   </si>
   <si>
     <t>B2-36</t>
   </si>
   <si>
-    <t>B2-D27b</t>
+    <t>B2-D27a</t>
   </si>
   <si>
     <t>B2-37</t>
   </si>
   <si>
-    <t>B2-D27a</t>
+    <t>B2-D42b</t>
   </si>
   <si>
     <t>B2-38</t>
   </si>
   <si>
-    <t>B2-D42b</t>
+    <t>B2-D42a</t>
   </si>
   <si>
     <t>B2-39</t>
   </si>
   <si>
-    <t>B2-D42a</t>
+    <t>B2-D39b</t>
   </si>
   <si>
     <t>B2-40</t>
   </si>
   <si>
-    <t>B2-D39b</t>
+    <t>B2-D39a</t>
   </si>
   <si>
     <t>B2-41</t>
   </si>
   <si>
-    <t>B2-D39a</t>
+    <t>B2-D28a</t>
   </si>
   <si>
     <t>B2-42</t>
   </si>
   <si>
-    <t>B2-D28a</t>
+    <t>B2-D28b</t>
   </si>
   <si>
     <t>B2-43</t>
   </si>
   <si>
-    <t>B2-D28b</t>
+    <t>B2-D47a</t>
   </si>
   <si>
     <t>B2-44</t>
   </si>
   <si>
-    <t>B2-D47a</t>
+    <t>B2-D47b</t>
   </si>
   <si>
     <t>B2-45</t>
   </si>
   <si>
-    <t>B2-D47b</t>
+    <t>B2-D49a</t>
   </si>
   <si>
     <t>B2-46</t>
   </si>
   <si>
-    <t>B2-D49a</t>
+    <t>B2-D49b</t>
   </si>
   <si>
     <t>B2-47</t>
   </si>
   <si>
-    <t>B2-D49b</t>
+    <t>B2-D16a</t>
   </si>
   <si>
     <t>B2-48</t>
   </si>
   <si>
-    <t>B2-D16a</t>
+    <t>B2-D16b</t>
   </si>
   <si>
     <t>B2-49</t>
   </si>
   <si>
-    <t>B2-D16b</t>
+    <t>T23-04</t>
   </si>
   <si>
     <t>B2-50</t>
@@ -1278,13 +1278,13 @@
     <t>B3-01</t>
   </si>
   <si>
-    <t>B3-D02b, B3-D02a</t>
+    <t>T23-02, T23-03</t>
   </si>
   <si>
     <t>B3-02</t>
   </si>
   <si>
-    <t>B3-D13b, B3-D13a</t>
+    <t>T23-01, T23-04</t>
   </si>
   <si>
     <t>B3-03</t>
@@ -5190,19 +5190,19 @@
       </c>
       <c r="F28" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 2",GiaCuong_TaiNeo!$K$4:$K$301)</f>
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="G28" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 3",GiaCuong_TaiNeo!$K$4:$K$301)</f>
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H28" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 4",GiaCuong_TaiNeo!$K$4:$K$301)</f>
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="I28" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 5",GiaCuong_TaiNeo!$K$4:$K$301)</f>
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="J28" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 6",GiaCuong_TaiNeo!$K$4:$K$301)</f>
@@ -5210,11 +5210,11 @@
       </c>
       <c r="K28" s="8">
         <f t="shared" ref="K28:K35" si="4">SUM(E28:J28)</f>
-        <v>730</v>
+        <v>617</v>
       </c>
       <c r="L28" s="8">
         <f>K28</f>
-        <v>730</v>
+        <v>617</v>
       </c>
       <c r="M28" s="7" t="s">
         <v>40</v>
@@ -5240,19 +5240,19 @@
       </c>
       <c r="F29" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 2",GiaCuong_TaiNeo!$M$4:$M$301)</f>
-        <v>2534.9979999999996</v>
+        <v>1924.4120000000003</v>
       </c>
       <c r="G29" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 3",GiaCuong_TaiNeo!$M$4:$M$301)</f>
-        <v>570</v>
+        <v>686.31999999999994</v>
       </c>
       <c r="H29" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 4",GiaCuong_TaiNeo!$M$4:$M$301)</f>
-        <v>1850.1470000000002</v>
+        <v>1296.0619999999999</v>
       </c>
       <c r="I29" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 5",GiaCuong_TaiNeo!$M$4:$M$301)</f>
-        <v>1837.2539999999999</v>
+        <v>1241.644</v>
       </c>
       <c r="J29" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 6",GiaCuong_TaiNeo!$M$4:$M$301)</f>
@@ -5260,11 +5260,11 @@
       </c>
       <c r="K29" s="8">
         <f t="shared" si="4"/>
-        <v>10738.710999999999</v>
+        <v>9094.75</v>
       </c>
       <c r="L29" s="8">
         <f>K29</f>
-        <v>10738.710999999999</v>
+        <v>9094.75</v>
       </c>
       <c r="M29" s="7" t="s">
         <v>40</v>
@@ -5290,19 +5290,19 @@
       </c>
       <c r="F30" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 2",GiaCuong_TaiNeo!$N$4:$N$301)</f>
-        <v>515</v>
+        <v>388</v>
       </c>
       <c r="G30" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 3",GiaCuong_TaiNeo!$N$4:$N$301)</f>
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="H30" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 4",GiaCuong_TaiNeo!$N$4:$N$301)</f>
-        <v>371</v>
+        <v>260</v>
       </c>
       <c r="I30" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 5",GiaCuong_TaiNeo!$N$4:$N$301)</f>
-        <v>366</v>
+        <v>247</v>
       </c>
       <c r="J30" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 6",GiaCuong_TaiNeo!$N$4:$N$301)</f>
@@ -5310,11 +5310,11 @@
       </c>
       <c r="K30" s="8">
         <f t="shared" si="4"/>
-        <v>2160</v>
+        <v>1828</v>
       </c>
       <c r="L30" s="8">
         <f>K30</f>
-        <v>2160</v>
+        <v>1828</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>40</v>
@@ -5340,19 +5340,19 @@
       </c>
       <c r="F31" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 2",GiaCuong_TaiNeo!$O$4:$O$301)</f>
-        <v>339</v>
+        <v>257</v>
       </c>
       <c r="G31" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 3",GiaCuong_TaiNeo!$O$4:$O$301)</f>
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H31" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 4",GiaCuong_TaiNeo!$O$4:$O$301)</f>
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="I31" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 5",GiaCuong_TaiNeo!$O$4:$O$301)</f>
-        <v>242</v>
+        <v>163</v>
       </c>
       <c r="J31" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 6",GiaCuong_TaiNeo!$O$4:$O$301)</f>
@@ -5360,11 +5360,11 @@
       </c>
       <c r="K31" s="8">
         <f t="shared" si="4"/>
-        <v>1430</v>
+        <v>1211</v>
       </c>
       <c r="L31" s="8">
         <f>ROUNDUP(K31*(1+GiaDinh!$C$14/100),0)</f>
-        <v>1473</v>
+        <v>1248</v>
       </c>
       <c r="M31" s="7" t="s">
         <v>35</v>
@@ -5388,19 +5388,19 @@
       </c>
       <c r="F32" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 2",GiaCuong_TaiNeo!$P$4:$P$301)</f>
-        <v>2047</v>
+        <v>1544</v>
       </c>
       <c r="G32" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 3",GiaCuong_TaiNeo!$P$4:$P$301)</f>
-        <v>466</v>
+        <v>556</v>
       </c>
       <c r="H32" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 4",GiaCuong_TaiNeo!$P$4:$P$301)</f>
-        <v>1511</v>
+        <v>1052</v>
       </c>
       <c r="I32" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 5",GiaCuong_TaiNeo!$P$4:$P$301)</f>
-        <v>1527</v>
+        <v>1026</v>
       </c>
       <c r="J32" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 6",GiaCuong_TaiNeo!$P$4:$P$301)</f>
@@ -5408,11 +5408,11 @@
       </c>
       <c r="K32" s="8">
         <f t="shared" si="4"/>
-        <v>8751</v>
+        <v>7378</v>
       </c>
       <c r="L32" s="8">
         <f>ROUNDUP(K32*(1+GiaDinh!$C$14/100),0)</f>
-        <v>9014</v>
+        <v>7600</v>
       </c>
       <c r="M32" s="7" t="s">
         <v>40</v>
@@ -5438,19 +5438,19 @@
       </c>
       <c r="F33" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 2",GiaCuong_TaiNeo!$Q$4:$Q$301)</f>
-        <v>4094</v>
+        <v>3088</v>
       </c>
       <c r="G33" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 3",GiaCuong_TaiNeo!$Q$4:$Q$301)</f>
-        <v>932</v>
+        <v>1112</v>
       </c>
       <c r="H33" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 4",GiaCuong_TaiNeo!$Q$4:$Q$301)</f>
-        <v>3022</v>
+        <v>2104</v>
       </c>
       <c r="I33" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 5",GiaCuong_TaiNeo!$Q$4:$Q$301)</f>
-        <v>3054</v>
+        <v>2052</v>
       </c>
       <c r="J33" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 6",GiaCuong_TaiNeo!$Q$4:$Q$301)</f>
@@ -5458,11 +5458,11 @@
       </c>
       <c r="K33" s="8">
         <f t="shared" si="4"/>
-        <v>17502</v>
+        <v>14756</v>
       </c>
       <c r="L33" s="8">
         <f>ROUNDUP(K33*(1+GiaDinh!$C$14/100),0)</f>
-        <v>18028</v>
+        <v>15199</v>
       </c>
       <c r="M33" s="7" t="s">
         <v>35</v>
@@ -5488,19 +5488,19 @@
       </c>
       <c r="F34" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 2",GiaCuong_TaiNeo!$R$4:$R$301)</f>
-        <v>2047</v>
+        <v>1544</v>
       </c>
       <c r="G34" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 3",GiaCuong_TaiNeo!$R$4:$R$301)</f>
-        <v>466</v>
+        <v>556</v>
       </c>
       <c r="H34" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 4",GiaCuong_TaiNeo!$R$4:$R$301)</f>
-        <v>1511</v>
+        <v>1052</v>
       </c>
       <c r="I34" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 5",GiaCuong_TaiNeo!$R$4:$R$301)</f>
-        <v>1527</v>
+        <v>1026</v>
       </c>
       <c r="J34" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 6",GiaCuong_TaiNeo!$R$4:$R$301)</f>
@@ -5508,11 +5508,11 @@
       </c>
       <c r="K34" s="8">
         <f t="shared" si="4"/>
-        <v>8751</v>
+        <v>7378</v>
       </c>
       <c r="L34" s="8">
         <f>ROUNDUP(K34*(1+GiaDinh!$C$14/100),0)</f>
-        <v>9014</v>
+        <v>7600</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>35</v>
@@ -5538,19 +5538,19 @@
       </c>
       <c r="F35" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 2",GiaCuong_TaiNeo!$S$4:$S$301)</f>
-        <v>7630.3439800000051</v>
+        <v>5792.4801199999893</v>
       </c>
       <c r="G35" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 3",GiaCuong_TaiNeo!$S$4:$S$301)</f>
-        <v>1715.7000000000012</v>
+        <v>2065.8232000000016</v>
       </c>
       <c r="H35" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 4",GiaCuong_TaiNeo!$S$4:$S$301)</f>
-        <v>5568.9424700000027</v>
+        <v>3901.1466200000013</v>
       </c>
       <c r="I35" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 5",GiaCuong_TaiNeo!$S$4:$S$301)</f>
-        <v>5530.1345400000037</v>
+        <v>3737.3484400000007</v>
       </c>
       <c r="J35" s="8">
         <f>SUMIF(GiaCuong_TaiNeo!$A$4:$A$301,"BÈ 6",GiaCuong_TaiNeo!$S$4:$S$301)</f>
@@ -5558,11 +5558,11 @@
       </c>
       <c r="K35" s="8">
         <f t="shared" si="4"/>
-        <v>32323.520110000019</v>
+        <v>27375.197499999998</v>
       </c>
       <c r="L35" s="8">
         <f>K35</f>
-        <v>32323.520110000019</v>
+        <v>27375.197499999998</v>
       </c>
       <c r="M35" s="7" t="s">
         <v>35</v>
@@ -6571,10 +6571,10 @@
         <v>43</v>
       </c>
       <c r="D22" s="8">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E22" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F22" s="8">
         <v>22</v>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="I22" s="8">
         <f t="shared" si="0"/>
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>145</v>
@@ -6604,10 +6604,10 @@
         <v>0</v>
       </c>
       <c r="D23" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E23" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" s="8">
         <v>14</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="I23" s="8">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>148</v>
@@ -11197,11 +11197,11 @@
         <v>2</v>
       </c>
       <c r="F69" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G69" s="11">
         <f>2*F69*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H69" s="7">
         <v>12</v>
@@ -11212,40 +11212,40 @@
       </c>
       <c r="J69" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K69" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L69" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M69" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N69" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O69" s="7">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P69" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q69" s="7">
         <f t="shared" si="8"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R69" s="7">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S69" s="12">
         <f>M69*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -11265,11 +11265,11 @@
         <v>2</v>
       </c>
       <c r="F70" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G70" s="11">
         <f>2*F70*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H70" s="7">
         <v>12</v>
@@ -11280,40 +11280,40 @@
       </c>
       <c r="J70" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K70" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L70" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M70" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N70" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O70" s="7">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P70" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q70" s="7">
         <f t="shared" si="8"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R70" s="7">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S70" s="12">
         <f>M70*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="71" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -11333,11 +11333,11 @@
         <v>2</v>
       </c>
       <c r="F71" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G71" s="11">
         <f>2*F71*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H71" s="7">
         <v>12</v>
@@ -11348,40 +11348,40 @@
       </c>
       <c r="J71" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K71" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L71" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M71" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N71" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O71" s="7">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P71" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q71" s="7">
         <f t="shared" si="8"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R71" s="7">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S71" s="12">
         <f>M71*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -11401,11 +11401,11 @@
         <v>3</v>
       </c>
       <c r="F72" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G72" s="11">
         <f>3*F72*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H72" s="7">
         <v>12</v>
@@ -11416,40 +11416,40 @@
       </c>
       <c r="J72" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K72" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L72" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M72" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N72" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O72" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P72" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q72" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R72" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S72" s="12">
         <f>M72*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -11469,11 +11469,11 @@
         <v>3</v>
       </c>
       <c r="F73" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G73" s="11">
         <f>3*F73*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H73" s="7">
         <v>11</v>
@@ -11537,11 +11537,11 @@
         <v>3</v>
       </c>
       <c r="F74" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G74" s="11">
         <f>3*F74*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H74" s="7">
         <v>12</v>
@@ -11552,40 +11552,40 @@
       </c>
       <c r="J74" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K74" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L74" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M74" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N74" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O74" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P74" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q74" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R74" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S74" s="12">
         <f>M74*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -11605,11 +11605,11 @@
         <v>3</v>
       </c>
       <c r="F75" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G75" s="11">
         <f>1*F75*GiaDinh!$C$18*GiaDinh!$C$17+309.6*GiaDinh!$C$17</f>
-        <v>473.91600000000005</v>
+        <v>451.48800000000006</v>
       </c>
       <c r="H75" s="7">
         <v>12</v>
@@ -11673,7 +11673,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G76" s="11">
         <f>0*F76*GiaDinh!$C$18*GiaDinh!$C$17+309.6*GiaDinh!$C$17</f>
@@ -11741,11 +11741,11 @@
         <v>4</v>
       </c>
       <c r="F77" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G77" s="11">
         <f>2*F77*GiaDinh!$C$18*GiaDinh!$C$17+309.6*GiaDinh!$C$17</f>
-        <v>576.31200000000001</v>
+        <v>531.45600000000002</v>
       </c>
       <c r="H77" s="7">
         <v>12</v>
@@ -11809,11 +11809,11 @@
         <v>2</v>
       </c>
       <c r="F78" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G78" s="11">
         <f>2*F78*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H78" s="7">
         <v>12</v>
@@ -11824,40 +11824,40 @@
       </c>
       <c r="J78" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L78" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M78" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N78" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O78" s="7">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P78" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q78" s="7">
         <f t="shared" si="8"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R78" s="7">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S78" s="12">
         <f>M78*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -11877,11 +11877,11 @@
         <v>3</v>
       </c>
       <c r="F79" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G79" s="11">
         <f>3*F79*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H79" s="7">
         <v>12</v>
@@ -11892,40 +11892,40 @@
       </c>
       <c r="J79" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K79" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L79" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M79" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N79" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O79" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P79" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q79" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R79" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S79" s="12">
         <f>M79*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -11945,11 +11945,11 @@
         <v>3</v>
       </c>
       <c r="F80" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G80" s="11">
         <f>3*F80*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H80" s="7">
         <v>11</v>
@@ -11970,10 +11970,10 @@
         <v>ĐỦ</v>
       </c>
       <c r="M80" s="11">
-        <v>55.777000000000001</v>
+        <v>56.832999999999998</v>
       </c>
       <c r="N80" s="7">
-        <f>ROUNDUP(13.944/GiaDinh!$C$5-0.0005,0)+ROUNDUP(13.944/GiaDinh!$C$5-0.0005,0)+ROUNDUP(13.944/GiaDinh!$C$5-0.0005,0)+ROUNDUP(13.944/GiaDinh!$C$5-0.0005,0)</f>
+        <f>ROUNDUP(13.944/GiaDinh!$C$5-0.0005,0)+ROUNDUP(13.944/GiaDinh!$C$5-0.0005,0)+ROUNDUP(13.944/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
         <v>12</v>
       </c>
       <c r="O80" s="7">
@@ -11981,19 +11981,19 @@
         <v>8</v>
       </c>
       <c r="P80" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q80" s="7">
         <f t="shared" si="8"/>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R80" s="7">
         <f t="shared" si="9"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S80" s="12">
         <f>M80*GiaDinh!$C$7</f>
-        <v>167.88876999999999</v>
+        <v>171.06732999999997</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -12013,11 +12013,11 @@
         <v>3</v>
       </c>
       <c r="F81" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G81" s="11">
         <f>3*F81*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H81" s="7">
         <v>12</v>
@@ -12028,40 +12028,40 @@
       </c>
       <c r="J81" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K81" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L81" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M81" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N81" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O81" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P81" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q81" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R81" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S81" s="12">
         <f>M81*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -12081,11 +12081,11 @@
         <v>3</v>
       </c>
       <c r="F82" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G82" s="11">
         <f>3*F82*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H82" s="7">
         <v>12</v>
@@ -12096,40 +12096,40 @@
       </c>
       <c r="J82" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K82" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L82" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M82" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N82" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O82" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P82" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q82" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R82" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S82" s="12">
         <f>M82*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -12149,11 +12149,11 @@
         <v>5</v>
       </c>
       <c r="F83" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G83" s="11">
-        <f>5*F83*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>511.97999999999996</v>
+        <f>2*F83*GiaDinh!$C$18*GiaDinh!$C$17+464.4*GiaDinh!$C$17</f>
+        <v>717.21600000000001</v>
       </c>
       <c r="H83" s="7">
         <v>12</v>
@@ -12164,40 +12164,40 @@
       </c>
       <c r="J83" s="7">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K83" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L83" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M83" s="11">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="N83" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>21</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>27</v>
       </c>
       <c r="O83" s="7">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P83" s="7">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="Q83" s="7">
         <f t="shared" si="8"/>
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="R83" s="7">
         <f t="shared" si="9"/>
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="S83" s="12">
         <f>M83*GiaDinh!$C$7</f>
-        <v>316.04999999999995</v>
+        <v>406.34999999999997</v>
       </c>
     </row>
     <row r="84" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -12214,21 +12214,21 @@
         <v>336</v>
       </c>
       <c r="E84" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G84" s="11">
-        <f>1*F84*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <f>2*F84*GiaDinh!$C$18*GiaDinh!$C$17</f>
+        <v>159.93600000000001</v>
       </c>
       <c r="H84" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I84" s="11">
         <f>H84*GiaDinh!$C$16</f>
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J84" s="7">
         <f t="shared" si="5"/>
@@ -12253,15 +12253,15 @@
         <v>4</v>
       </c>
       <c r="P84" s="7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q84" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="R84" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S84" s="12">
         <f>M84*GiaDinh!$C$7</f>
@@ -12282,21 +12282,21 @@
         <v>338</v>
       </c>
       <c r="E85" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G85" s="11">
-        <f>2*F85*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <f>3*F85*GiaDinh!$C$18*GiaDinh!$C$17</f>
+        <v>239.904</v>
       </c>
       <c r="H85" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I85" s="11">
         <f>H85*GiaDinh!$C$16</f>
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="J85" s="7">
         <f t="shared" si="5"/>
@@ -12321,15 +12321,15 @@
         <v>6</v>
       </c>
       <c r="P85" s="7">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q85" s="7">
         <f t="shared" si="8"/>
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="R85" s="7">
         <f t="shared" si="9"/>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="S85" s="12">
         <f>M85*GiaDinh!$C$7</f>
@@ -12350,14 +12350,14 @@
         <v>340</v>
       </c>
       <c r="E86" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F86" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G86" s="11">
-        <f>3*F86*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <f>1*F86*GiaDinh!$C$18*GiaDinh!$C$17</f>
+        <v>79.968000000000004</v>
       </c>
       <c r="H86" s="7">
         <v>12</v>
@@ -12368,40 +12368,40 @@
       </c>
       <c r="J86" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K86" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L86" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M86" s="11">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="N86" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O86" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P86" s="7">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="Q86" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="R86" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="S86" s="12">
         <f>M86*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -12418,14 +12418,14 @@
         <v>342</v>
       </c>
       <c r="E87" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F87" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G87" s="11">
-        <f>1*F87*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <f>3*F87*GiaDinh!$C$18*GiaDinh!$C$17</f>
+        <v>239.904</v>
       </c>
       <c r="H87" s="7">
         <v>12</v>
@@ -12436,40 +12436,40 @@
       </c>
       <c r="J87" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K87" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M87" s="11">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N87" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O87" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P87" s="7">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q87" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="R87" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S87" s="12">
         <f>M87*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -12489,11 +12489,11 @@
         <v>3</v>
       </c>
       <c r="F88" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G88" s="11">
         <f>3*F88*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H88" s="7">
         <v>12</v>
@@ -12504,40 +12504,40 @@
       </c>
       <c r="J88" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K88" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L88" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M88" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N88" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O88" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P88" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q88" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R88" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S88" s="12">
         <f>M88*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -12557,11 +12557,11 @@
         <v>3</v>
       </c>
       <c r="F89" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G89" s="11">
         <f>3*F89*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H89" s="7">
         <v>12</v>
@@ -12572,40 +12572,40 @@
       </c>
       <c r="J89" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K89" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L89" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M89" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N89" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O89" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P89" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q89" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R89" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S89" s="12">
         <f>M89*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -12625,11 +12625,11 @@
         <v>3</v>
       </c>
       <c r="F90" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G90" s="11">
         <f>3*F90*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H90" s="7">
         <v>12</v>
@@ -12640,43 +12640,43 @@
       </c>
       <c r="J90" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K90" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L90" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M90" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N90" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O90" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P90" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q90" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R90" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S90" s="12">
         <f>M90*GiaDinh!$C$7</f>
-        <v>180.6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
+        <v>135.44999999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" ht="31" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>7</v>
       </c>
@@ -12690,14 +12690,14 @@
         <v>350</v>
       </c>
       <c r="E91" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G91" s="11">
-        <f>3*F91*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <f>4*F91*GiaDinh!$C$18*GiaDinh!$C$17</f>
+        <v>319.87200000000001</v>
       </c>
       <c r="H91" s="7">
         <v>12</v>
@@ -12744,7 +12744,7 @@
         <v>180.6</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="31" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>7</v>
       </c>
@@ -12758,14 +12758,14 @@
         <v>352</v>
       </c>
       <c r="E92" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F92" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G92" s="11">
-        <f>4*F92*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>409.584</v>
+        <f>2*F92*GiaDinh!$C$18*GiaDinh!$C$17</f>
+        <v>159.93600000000001</v>
       </c>
       <c r="H92" s="7">
         <v>12</v>
@@ -12776,40 +12776,40 @@
       </c>
       <c r="J92" s="7">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K92" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L92" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M92" s="11">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="N92" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>15</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O92" s="7">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P92" s="7">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="Q92" s="7">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="R92" s="7">
         <f t="shared" si="9"/>
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="S92" s="12">
         <f>M92*GiaDinh!$C$7</f>
-        <v>225.74999999999997</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -12826,14 +12826,14 @@
         <v>354</v>
       </c>
       <c r="E93" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G93" s="11">
-        <f>2*F93*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <f>3*F93*GiaDinh!$C$18*GiaDinh!$C$17</f>
+        <v>239.904</v>
       </c>
       <c r="H93" s="7">
         <v>12</v>
@@ -12897,11 +12897,11 @@
         <v>3</v>
       </c>
       <c r="F94" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G94" s="11">
         <f>3*F94*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H94" s="7">
         <v>12</v>
@@ -12912,40 +12912,40 @@
       </c>
       <c r="J94" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K94" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L94" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M94" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N94" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O94" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P94" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q94" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R94" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S94" s="12">
         <f>M94*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="95" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -12965,11 +12965,11 @@
         <v>3</v>
       </c>
       <c r="F95" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G95" s="11">
         <f>3*F95*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H95" s="7">
         <v>12</v>
@@ -12980,40 +12980,40 @@
       </c>
       <c r="J95" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K95" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L95" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M95" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N95" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O95" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P95" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q95" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R95" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S95" s="12">
         <f>M95*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13033,18 +13033,18 @@
         <v>3</v>
       </c>
       <c r="F96" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G96" s="11">
         <f>3*F96*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H96" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I96" s="11">
         <f>H96*GiaDinh!$C$16</f>
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J96" s="7">
         <f t="shared" si="5"/>
@@ -13069,15 +13069,15 @@
         <v>8</v>
       </c>
       <c r="P96" s="7">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q96" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="R96" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="S96" s="12">
         <f>M96*GiaDinh!$C$7</f>
@@ -13101,55 +13101,55 @@
         <v>3</v>
       </c>
       <c r="F97" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G97" s="11">
         <f>3*F97*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H97" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I97" s="11">
         <f>H97*GiaDinh!$C$16</f>
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J97" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K97" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L97" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M97" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N97" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O97" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P97" s="7">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Q97" s="7">
         <f t="shared" si="8"/>
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="R97" s="7">
         <f t="shared" si="9"/>
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="S97" s="12">
         <f>M97*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="98" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13169,11 +13169,11 @@
         <v>3</v>
       </c>
       <c r="F98" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G98" s="11">
         <f>3*F98*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <v>239.904</v>
       </c>
       <c r="H98" s="7">
         <v>12</v>
@@ -13184,40 +13184,40 @@
       </c>
       <c r="J98" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K98" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L98" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M98" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N98" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O98" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P98" s="7">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q98" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R98" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S98" s="12">
         <f>M98*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13228,64 +13228,64 @@
         <v>365</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>366</v>
       </c>
       <c r="E99" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F99" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G99" s="11">
-        <f>3*F99*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>307.18799999999999</v>
+        <f>1*F99*GiaDinh!$C$18*GiaDinh!$C$17</f>
+        <v>79.968000000000004</v>
       </c>
       <c r="H99" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I99" s="11">
         <f>H99*GiaDinh!$C$16</f>
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J99" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K99" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L99" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M99" s="11">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="N99" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O99" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P99" s="7">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="Q99" s="7">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="R99" s="7">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="S99" s="12">
         <f>M99*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="100" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13305,11 +13305,11 @@
         <v>1</v>
       </c>
       <c r="F100" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G100" s="11">
         <f>1*F100*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H100" s="7">
         <v>13</v>
@@ -13320,40 +13320,40 @@
       </c>
       <c r="J100" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K100" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L100" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M100" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N100" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O100" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P100" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q100" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R100" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S100" s="12">
         <f>M100*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="101" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13373,11 +13373,11 @@
         <v>1</v>
       </c>
       <c r="F101" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G101" s="11">
         <f>1*F101*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H101" s="7">
         <v>13</v>
@@ -13388,40 +13388,40 @@
       </c>
       <c r="J101" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K101" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L101" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M101" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N101" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O101" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P101" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q101" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R101" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S101" s="12">
         <f>M101*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="102" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13441,11 +13441,11 @@
         <v>1</v>
       </c>
       <c r="F102" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G102" s="11">
         <f>1*F102*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H102" s="7">
         <v>13</v>
@@ -13456,40 +13456,40 @@
       </c>
       <c r="J102" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K102" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L102" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M102" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N102" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O102" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P102" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q102" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R102" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S102" s="12">
         <f>M102*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="103" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13509,11 +13509,11 @@
         <v>1</v>
       </c>
       <c r="F103" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G103" s="11">
         <f>1*F103*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H103" s="7">
         <v>13</v>
@@ -13524,40 +13524,40 @@
       </c>
       <c r="J103" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K103" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L103" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M103" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N103" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O103" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P103" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q103" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R103" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S103" s="12">
         <f>M103*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="104" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13577,11 +13577,11 @@
         <v>1</v>
       </c>
       <c r="F104" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G104" s="11">
         <f>1*F104*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H104" s="7">
         <v>13</v>
@@ -13592,40 +13592,40 @@
       </c>
       <c r="J104" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K104" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L104" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M104" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N104" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O104" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P104" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q104" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R104" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S104" s="12">
         <f>M104*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="105" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13645,11 +13645,11 @@
         <v>1</v>
       </c>
       <c r="F105" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G105" s="11">
         <f>1*F105*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H105" s="7">
         <v>13</v>
@@ -13660,40 +13660,40 @@
       </c>
       <c r="J105" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K105" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L105" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M105" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N105" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O105" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P105" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q105" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R105" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S105" s="12">
         <f>M105*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="106" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13713,11 +13713,11 @@
         <v>1</v>
       </c>
       <c r="F106" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G106" s="11">
         <f>1*F106*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H106" s="7">
         <v>13</v>
@@ -13728,40 +13728,40 @@
       </c>
       <c r="J106" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K106" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L106" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M106" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N106" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O106" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P106" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q106" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R106" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S106" s="12">
         <f>M106*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="107" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13781,55 +13781,55 @@
         <v>1</v>
       </c>
       <c r="F107" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G107" s="11">
         <f>1*F107*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H107" s="7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I107" s="11">
         <f>H107*GiaDinh!$C$16</f>
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="J107" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K107" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L107" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M107" s="11">
-        <v>30</v>
+        <v>19.497</v>
       </c>
       <c r="N107" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <f>ROUNDUP(6.499/GiaDinh!$C$5-0.0005,0)+ROUNDUP(6.499/GiaDinh!$C$5-0.0005,0)+ROUNDUP(6.499/GiaDinh!$C$5-0.0005,0)</f>
         <v>6</v>
       </c>
       <c r="O107" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P107" s="7">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Q107" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="R107" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="S107" s="12">
         <f>M107*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>58.685969999999998</v>
       </c>
     </row>
     <row r="108" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13849,55 +13849,55 @@
         <v>1</v>
       </c>
       <c r="F108" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G108" s="11">
         <f>1*F108*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H108" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I108" s="11">
         <f>H108*GiaDinh!$C$16</f>
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="J108" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K108" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L108" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M108" s="11">
-        <v>19.497</v>
+        <v>15</v>
       </c>
       <c r="N108" s="7">
-        <f>ROUNDUP(6.499/GiaDinh!$C$5-0.0005,0)+ROUNDUP(6.499/GiaDinh!$C$5-0.0005,0)+ROUNDUP(6.499/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O108" s="7">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P108" s="7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q108" s="7">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="R108" s="7">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S108" s="12">
         <f>M108*GiaDinh!$C$7</f>
-        <v>58.685969999999998</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="109" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13917,55 +13917,55 @@
         <v>1</v>
       </c>
       <c r="F109" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G109" s="11">
         <f>1*F109*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H109" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I109" s="11">
         <f>H109*GiaDinh!$C$16</f>
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="J109" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K109" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L109" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M109" s="11">
-        <v>36.499000000000002</v>
+        <v>15</v>
       </c>
       <c r="N109" s="7">
-        <f>ROUNDUP(6.499/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>8</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O109" s="7">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P109" s="7">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Q109" s="7">
         <f t="shared" si="8"/>
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="R109" s="7">
         <f t="shared" si="9"/>
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="S109" s="12">
         <f>M109*GiaDinh!$C$7</f>
-        <v>109.86199000000001</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="110" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -13985,11 +13985,11 @@
         <v>1</v>
       </c>
       <c r="F110" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G110" s="11">
         <f>1*F110*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H110" s="7">
         <v>12</v>
@@ -14000,40 +14000,40 @@
       </c>
       <c r="J110" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K110" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L110" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M110" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N110" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O110" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P110" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q110" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R110" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S110" s="12">
         <f>M110*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="111" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14053,11 +14053,11 @@
         <v>1</v>
       </c>
       <c r="F111" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G111" s="11">
         <f>1*F111*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H111" s="7">
         <v>12</v>
@@ -14068,40 +14068,40 @@
       </c>
       <c r="J111" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K111" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L111" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M111" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N111" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O111" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P111" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q111" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R111" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S111" s="12">
         <f>M111*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="112" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14121,11 +14121,11 @@
         <v>1</v>
       </c>
       <c r="F112" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G112" s="11">
         <f>1*F112*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H112" s="7">
         <v>12</v>
@@ -14136,40 +14136,40 @@
       </c>
       <c r="J112" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K112" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L112" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M112" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N112" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O112" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P112" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q112" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R112" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S112" s="12">
         <f>M112*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="113" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14189,11 +14189,11 @@
         <v>1</v>
       </c>
       <c r="F113" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G113" s="11">
         <f>1*F113*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H113" s="7">
         <v>12</v>
@@ -14204,40 +14204,40 @@
       </c>
       <c r="J113" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K113" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L113" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M113" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N113" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O113" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P113" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q113" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R113" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S113" s="12">
         <f>M113*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="114" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14257,11 +14257,11 @@
         <v>1</v>
       </c>
       <c r="F114" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G114" s="11">
         <f>1*F114*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H114" s="7">
         <v>12</v>
@@ -14272,40 +14272,40 @@
       </c>
       <c r="J114" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K114" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L114" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M114" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N114" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O114" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P114" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q114" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R114" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S114" s="12">
         <f>M114*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="115" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14325,11 +14325,11 @@
         <v>1</v>
       </c>
       <c r="F115" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G115" s="11">
         <f>1*F115*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H115" s="7">
         <v>12</v>
@@ -14340,40 +14340,40 @@
       </c>
       <c r="J115" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K115" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L115" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M115" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N115" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O115" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P115" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q115" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R115" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S115" s="12">
         <f>M115*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14393,11 +14393,11 @@
         <v>1</v>
       </c>
       <c r="F116" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G116" s="11">
         <f>1*F116*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H116" s="7">
         <v>12</v>
@@ -14408,40 +14408,40 @@
       </c>
       <c r="J116" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K116" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L116" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M116" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N116" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O116" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P116" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q116" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R116" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S116" s="12">
         <f>M116*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="117" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14461,11 +14461,11 @@
         <v>1</v>
       </c>
       <c r="F117" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G117" s="11">
-        <f>1*F117*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <f>0*F117*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
+        <v>185.76000000000002</v>
       </c>
       <c r="H117" s="7">
         <v>12</v>
@@ -14476,40 +14476,40 @@
       </c>
       <c r="J117" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K117" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L117" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M117" s="11">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N117" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>9</v>
       </c>
       <c r="O117" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P117" s="7">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q117" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="R117" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S117" s="12">
         <f>M117*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>135.44999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14529,55 +14529,55 @@
         <v>1</v>
       </c>
       <c r="F118" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G118" s="11">
         <f>1*F118*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H118" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I118" s="11">
         <f>H118*GiaDinh!$C$16</f>
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="J118" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K118" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L118" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M118" s="11">
-        <v>20.550999999999998</v>
+        <v>15</v>
       </c>
       <c r="N118" s="7">
-        <f>ROUNDUP(6.85/GiaDinh!$C$5-0.0005,0)+ROUNDUP(6.85/GiaDinh!$C$5-0.0005,0)+ROUNDUP(6.85/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O118" s="7">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P118" s="7">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q118" s="7">
         <f t="shared" si="8"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="R118" s="7">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="S118" s="12">
         <f>M118*GiaDinh!$C$7</f>
-        <v>61.858509999999988</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="119" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14597,55 +14597,55 @@
         <v>1</v>
       </c>
       <c r="F119" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G119" s="11">
         <f>1*F119*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H119" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I119" s="11">
         <f>H119*GiaDinh!$C$16</f>
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="J119" s="7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K119" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L119" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M119" s="11">
-        <v>20.550999999999998</v>
+        <v>15</v>
       </c>
       <c r="N119" s="7">
-        <f>ROUNDUP(6.85/GiaDinh!$C$5-0.0005,0)+ROUNDUP(6.85/GiaDinh!$C$5-0.0005,0)+ROUNDUP(6.85/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O119" s="7">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P119" s="7">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q119" s="7">
         <f t="shared" si="8"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="R119" s="7">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="S119" s="12">
         <f>M119*GiaDinh!$C$7</f>
-        <v>61.858509999999988</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="120" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14665,11 +14665,11 @@
         <v>1</v>
       </c>
       <c r="F120" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G120" s="11">
         <f>1*F120*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H120" s="7">
         <v>13</v>
@@ -14680,40 +14680,40 @@
       </c>
       <c r="J120" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K120" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L120" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M120" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N120" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O120" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P120" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q120" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R120" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S120" s="12">
         <f>M120*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14733,11 +14733,11 @@
         <v>1</v>
       </c>
       <c r="F121" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G121" s="11">
         <f>1*F121*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H121" s="7">
         <v>13</v>
@@ -14748,40 +14748,40 @@
       </c>
       <c r="J121" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K121" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L121" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M121" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N121" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O121" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P121" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q121" s="7">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R121" s="7">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S121" s="12">
         <f>M121*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="122" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14801,11 +14801,11 @@
         <v>1</v>
       </c>
       <c r="F122" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G122" s="11">
         <f>1*F122*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H122" s="7">
         <v>8</v>
@@ -14869,55 +14869,55 @@
         <v>1</v>
       </c>
       <c r="F123" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G123" s="11">
         <f>1*F123*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H123" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I123" s="11">
         <f>H123*GiaDinh!$C$16</f>
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="J123" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K123" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L123" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M123" s="11">
-        <v>24.041</v>
+        <v>15</v>
       </c>
       <c r="N123" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(9.041/GiaDinh!$C$5-0.0005,0)</f>
-        <v>5</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O123" s="7">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P123" s="7">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Q123" s="7">
         <f t="shared" si="8"/>
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="R123" s="7">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S123" s="12">
         <f>M123*GiaDinh!$C$7</f>
-        <v>72.363410000000002</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="124" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -14937,11 +14937,11 @@
         <v>2</v>
       </c>
       <c r="F124" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G124" s="11">
-        <f>2*F124*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>132.21599999999998</v>
+        <f>0*F124*GiaDinh!$C$18*GiaDinh!$C$17+309.6*GiaDinh!$C$17</f>
+        <v>371.52000000000004</v>
       </c>
       <c r="H124" s="7">
         <v>12</v>
@@ -14952,40 +14952,40 @@
       </c>
       <c r="J124" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K124" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L124" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M124" s="11">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="N124" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>15</v>
       </c>
       <c r="O124" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P124" s="7">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="Q124" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="R124" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="S124" s="12">
         <f>M124*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="125" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -15005,55 +15005,55 @@
         <v>2</v>
       </c>
       <c r="F125" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G125" s="11">
-        <f>2*F125*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>132.21599999999998</v>
+        <f>0*F125*GiaDinh!$C$18*GiaDinh!$C$17+309.6*GiaDinh!$C$17</f>
+        <v>371.52000000000004</v>
       </c>
       <c r="H125" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I125" s="11">
         <f>H125*GiaDinh!$C$16</f>
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J125" s="7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K125" s="7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L125" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M125" s="11">
-        <v>30</v>
+        <v>82.308999999999997</v>
       </c>
       <c r="N125" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(13.462/GiaDinh!$C$5-0.0005,0)+ROUNDUP(13.462/GiaDinh!$C$5-0.0005,0)+ROUNDUP(13.462/GiaDinh!$C$5-0.0005,0)+ROUNDUP(13.462/GiaDinh!$C$5-0.0005,0)+ROUNDUP(13.462/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>18</v>
       </c>
       <c r="O125" s="7">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P125" s="7">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="Q125" s="7">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="R125" s="7">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="S125" s="12">
         <f>M125*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>247.75008999999997</v>
       </c>
     </row>
     <row r="126" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -15073,11 +15073,11 @@
         <v>2</v>
       </c>
       <c r="F126" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G126" s="11">
         <f>2*F126*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>132.21599999999998</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H126" s="7">
         <v>13</v>
@@ -15141,11 +15141,11 @@
         <v>2</v>
       </c>
       <c r="F127" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G127" s="11">
         <f>2*F127*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>132.21599999999998</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H127" s="7">
         <v>12</v>
@@ -15209,11 +15209,11 @@
         <v>4</v>
       </c>
       <c r="F128" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G128" s="11">
         <f>4*F128*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>264.43199999999996</v>
+        <v>319.87200000000001</v>
       </c>
       <c r="H128" s="7">
         <v>11</v>
@@ -15224,40 +15224,40 @@
       </c>
       <c r="J128" s="7">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K128" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L128" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M128" s="11">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N128" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>12</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>15</v>
       </c>
       <c r="O128" s="7">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P128" s="7">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="Q128" s="7">
         <f t="shared" si="8"/>
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="R128" s="7">
         <f t="shared" si="9"/>
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="S128" s="12">
         <f>M128*GiaDinh!$C$7</f>
-        <v>180.6</v>
+        <v>225.74999999999997</v>
       </c>
     </row>
     <row r="129" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -15277,11 +15277,11 @@
         <v>2</v>
       </c>
       <c r="F129" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G129" s="11">
         <f>2*F129*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>132.21599999999998</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H129" s="7">
         <v>13</v>
@@ -15345,55 +15345,55 @@
         <v>1</v>
       </c>
       <c r="F130" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G130" s="11">
         <f>1*F130*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H130" s="7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I130" s="11">
         <f>H130*GiaDinh!$C$16</f>
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="J130" s="7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K130" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L130" s="7" t="str">
         <f t="shared" si="6"/>
         <v>ĐỦ</v>
       </c>
       <c r="M130" s="11">
-        <v>15</v>
+        <v>19.010999999999999</v>
       </c>
       <c r="N130" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>3</v>
+        <f>ROUNDUP(9.506/GiaDinh!$C$5-0.0005,0)+ROUNDUP(9.506/GiaDinh!$C$5-0.0005,0)</f>
+        <v>4</v>
       </c>
       <c r="O130" s="7">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="P130" s="7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q130" s="7">
         <f t="shared" si="8"/>
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="R130" s="7">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="S130" s="12">
         <f>M130*GiaDinh!$C$7</f>
-        <v>45.15</v>
+        <v>57.223109999999991</v>
       </c>
     </row>
     <row r="131" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -15413,11 +15413,11 @@
         <v>1</v>
       </c>
       <c r="F131" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G131" s="11">
         <f>1*F131*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H131" s="7">
         <v>13</v>
@@ -15481,11 +15481,11 @@
         <v>1</v>
       </c>
       <c r="F132" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G132" s="11">
         <f>1*F132*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H132" s="7">
         <v>13</v>
@@ -15549,11 +15549,11 @@
         <v>1</v>
       </c>
       <c r="F133" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G133" s="11">
         <f>1*F133*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H133" s="7">
         <v>13</v>
@@ -15617,11 +15617,11 @@
         <v>1</v>
       </c>
       <c r="F134" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G134" s="11">
         <f>1*F134*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H134" s="7">
         <v>13</v>
@@ -15685,11 +15685,11 @@
         <v>1</v>
       </c>
       <c r="F135" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G135" s="11">
         <f>1*F135*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H135" s="7">
         <v>13</v>
@@ -15753,11 +15753,11 @@
         <v>1</v>
       </c>
       <c r="F136" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G136" s="11">
         <f>1*F136*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H136" s="7">
         <v>13</v>
@@ -15821,11 +15821,11 @@
         <v>1</v>
       </c>
       <c r="F137" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G137" s="11">
         <f>1*F137*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H137" s="7">
         <v>13</v>
@@ -15889,11 +15889,11 @@
         <v>1</v>
       </c>
       <c r="F138" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G138" s="11">
         <f>1*F138*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H138" s="7">
         <v>13</v>
@@ -15957,11 +15957,11 @@
         <v>1</v>
       </c>
       <c r="F139" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G139" s="11">
         <f>1*F139*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H139" s="7">
         <v>13</v>
@@ -16025,11 +16025,11 @@
         <v>1</v>
       </c>
       <c r="F140" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G140" s="11">
         <f>1*F140*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H140" s="7">
         <v>12</v>
@@ -16093,11 +16093,11 @@
         <v>1</v>
       </c>
       <c r="F141" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G141" s="11">
         <f>1*F141*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H141" s="7">
         <v>12</v>
@@ -16161,11 +16161,11 @@
         <v>1</v>
       </c>
       <c r="F142" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G142" s="11">
         <f>1*F142*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H142" s="7">
         <v>12</v>
@@ -16229,11 +16229,11 @@
         <v>1</v>
       </c>
       <c r="F143" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G143" s="11">
         <f>1*F143*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H143" s="7">
         <v>12</v>
@@ -16297,11 +16297,11 @@
         <v>1</v>
       </c>
       <c r="F144" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G144" s="11">
         <f>1*F144*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H144" s="7">
         <v>12</v>
@@ -16365,11 +16365,11 @@
         <v>1</v>
       </c>
       <c r="F145" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G145" s="11">
         <f>1*F145*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H145" s="7">
         <v>12</v>
@@ -16433,11 +16433,11 @@
         <v>1</v>
       </c>
       <c r="F146" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G146" s="11">
         <f>1*F146*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H146" s="7">
         <v>12</v>
@@ -16501,11 +16501,11 @@
         <v>1</v>
       </c>
       <c r="F147" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G147" s="11">
         <f>1*F147*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H147" s="7">
         <v>12</v>
@@ -16569,11 +16569,11 @@
         <v>1</v>
       </c>
       <c r="F148" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G148" s="11">
         <f>1*F148*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H148" s="7">
         <v>12</v>
@@ -16637,11 +16637,11 @@
         <v>1</v>
       </c>
       <c r="F149" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G149" s="11">
         <f>1*F149*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H149" s="7">
         <v>12</v>
@@ -16705,11 +16705,11 @@
         <v>1</v>
       </c>
       <c r="F150" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G150" s="11">
         <f>1*F150*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H150" s="7">
         <v>12</v>
@@ -16773,11 +16773,11 @@
         <v>1</v>
       </c>
       <c r="F151" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G151" s="11">
         <f>1*F151*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H151" s="7">
         <v>12</v>
@@ -16841,11 +16841,11 @@
         <v>1</v>
       </c>
       <c r="F152" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G152" s="11">
         <f>1*F152*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H152" s="7">
         <v>12</v>
@@ -16909,11 +16909,11 @@
         <v>1</v>
       </c>
       <c r="F153" s="7">
-        <v>78.7</v>
+        <v>95.2</v>
       </c>
       <c r="G153" s="11">
         <f>1*F153*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>66.10799999999999</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H153" s="7">
         <v>12</v>
@@ -16977,11 +16977,11 @@
         <v>2</v>
       </c>
       <c r="F154" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G154" s="11">
         <f>2*F154*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H154" s="7">
         <v>12</v>
@@ -16992,40 +16992,40 @@
       </c>
       <c r="J154" s="7">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K154" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L154" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M154" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N154" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O154" s="7">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P154" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q154" s="7">
         <f t="shared" si="13"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R154" s="7">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S154" s="12">
         <f>M154*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="155" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17045,11 +17045,11 @@
         <v>2</v>
       </c>
       <c r="F155" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G155" s="11">
         <f>2*F155*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H155" s="7">
         <v>12</v>
@@ -17060,40 +17060,40 @@
       </c>
       <c r="J155" s="7">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K155" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L155" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M155" s="11">
-        <v>42.555999999999997</v>
+        <v>28.370999999999999</v>
       </c>
       <c r="N155" s="7">
-        <f>ROUNDUP(14.185/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.185/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.185/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(14.185/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.185/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O155" s="7">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P155" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q155" s="7">
         <f t="shared" si="13"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R155" s="7">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S155" s="12">
         <f>M155*GiaDinh!$C$7</f>
-        <v>128.09356</v>
+        <v>85.396709999999985</v>
       </c>
     </row>
     <row r="156" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17113,7 +17113,7 @@
         <v>1</v>
       </c>
       <c r="F156" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G156" s="11">
         <f>0*F156*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -17181,7 +17181,7 @@
         <v>1</v>
       </c>
       <c r="F157" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G157" s="11">
         <f>0*F157*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -17249,7 +17249,7 @@
         <v>1</v>
       </c>
       <c r="F158" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G158" s="11">
         <f>0*F158*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -17317,7 +17317,7 @@
         <v>2</v>
       </c>
       <c r="F159" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G159" s="11">
         <f>0*F159*GiaDinh!$C$18*GiaDinh!$C$17+309.6*GiaDinh!$C$17</f>
@@ -17385,7 +17385,7 @@
         <v>1</v>
       </c>
       <c r="F160" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G160" s="11">
         <f>0*F160*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -17453,11 +17453,11 @@
         <v>2</v>
       </c>
       <c r="F161" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G161" s="11">
         <f>2*F161*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H161" s="7">
         <v>12</v>
@@ -17468,40 +17468,40 @@
       </c>
       <c r="J161" s="7">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K161" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L161" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M161" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N161" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O161" s="7">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P161" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q161" s="7">
         <f t="shared" si="13"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R161" s="7">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S161" s="12">
         <f>M161*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="162" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17521,11 +17521,11 @@
         <v>2</v>
       </c>
       <c r="F162" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G162" s="11">
         <f>2*F162*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H162" s="7">
         <v>11</v>
@@ -17546,10 +17546,10 @@
         <v>ĐỦ</v>
       </c>
       <c r="M162" s="11">
-        <v>42.801000000000002</v>
+        <v>43.533999999999999</v>
       </c>
       <c r="N162" s="7">
-        <f>ROUNDUP(14.267/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.267/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.267/GiaDinh!$C$5-0.0005,0)</f>
+        <f>ROUNDUP(14.267/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.267/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
         <v>9</v>
       </c>
       <c r="O162" s="7">
@@ -17557,19 +17557,19 @@
         <v>6</v>
       </c>
       <c r="P162" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q162" s="7">
         <f t="shared" si="13"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R162" s="7">
         <f t="shared" si="14"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S162" s="12">
         <f>M162*GiaDinh!$C$7</f>
-        <v>128.83100999999999</v>
+        <v>131.03734</v>
       </c>
     </row>
     <row r="163" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17589,11 +17589,11 @@
         <v>2</v>
       </c>
       <c r="F163" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G163" s="11">
         <f>2*F163*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H163" s="7">
         <v>12</v>
@@ -17604,40 +17604,40 @@
       </c>
       <c r="J163" s="7">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K163" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L163" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M163" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N163" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O163" s="7">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P163" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q163" s="7">
         <f t="shared" si="13"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R163" s="7">
         <f t="shared" si="14"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S163" s="12">
         <f>M163*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="164" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17657,11 +17657,11 @@
         <v>1</v>
       </c>
       <c r="F164" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G164" s="11">
         <f>1*F164*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H164" s="7">
         <v>12</v>
@@ -17672,40 +17672,40 @@
       </c>
       <c r="J164" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K164" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L164" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M164" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N164" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O164" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P164" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q164" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R164" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S164" s="12">
         <f>M164*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="165" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17725,11 +17725,11 @@
         <v>1</v>
       </c>
       <c r="F165" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G165" s="11">
         <f>1*F165*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H165" s="7">
         <v>12</v>
@@ -17740,40 +17740,40 @@
       </c>
       <c r="J165" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K165" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L165" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M165" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N165" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O165" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P165" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q165" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R165" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S165" s="12">
         <f>M165*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="166" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17793,11 +17793,11 @@
         <v>1</v>
       </c>
       <c r="F166" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G166" s="11">
         <f>1*F166*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H166" s="7">
         <v>12</v>
@@ -17808,40 +17808,40 @@
       </c>
       <c r="J166" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K166" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L166" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M166" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N166" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O166" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P166" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q166" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R166" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S166" s="12">
         <f>M166*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="167" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17861,11 +17861,11 @@
         <v>1</v>
       </c>
       <c r="F167" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G167" s="11">
         <f>1*F167*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H167" s="7">
         <v>12</v>
@@ -17876,40 +17876,40 @@
       </c>
       <c r="J167" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K167" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L167" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M167" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N167" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O167" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P167" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q167" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R167" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S167" s="12">
         <f>M167*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="168" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17929,11 +17929,11 @@
         <v>1</v>
       </c>
       <c r="F168" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G168" s="11">
         <f>1*F168*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H168" s="7">
         <v>12</v>
@@ -17944,40 +17944,40 @@
       </c>
       <c r="J168" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K168" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L168" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M168" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N168" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O168" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P168" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q168" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R168" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S168" s="12">
         <f>M168*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="169" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -17997,11 +17997,11 @@
         <v>1</v>
       </c>
       <c r="F169" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G169" s="11">
         <f>1*F169*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H169" s="7">
         <v>12</v>
@@ -18012,40 +18012,40 @@
       </c>
       <c r="J169" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K169" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L169" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M169" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N169" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O169" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P169" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q169" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R169" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S169" s="12">
         <f>M169*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="170" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18065,11 +18065,11 @@
         <v>1</v>
       </c>
       <c r="F170" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G170" s="11">
         <f>1*F170*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H170" s="7">
         <v>13</v>
@@ -18080,40 +18080,40 @@
       </c>
       <c r="J170" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K170" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L170" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M170" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N170" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O170" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P170" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q170" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R170" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S170" s="12">
         <f>M170*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="171" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18133,11 +18133,11 @@
         <v>1</v>
       </c>
       <c r="F171" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G171" s="11">
         <f>1*F171*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H171" s="7">
         <v>13</v>
@@ -18148,40 +18148,40 @@
       </c>
       <c r="J171" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K171" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L171" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M171" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N171" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O171" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P171" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q171" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R171" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S171" s="12">
         <f>M171*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="172" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18201,11 +18201,11 @@
         <v>1</v>
       </c>
       <c r="F172" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G172" s="11">
         <f>1*F172*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H172" s="7">
         <v>13</v>
@@ -18216,40 +18216,40 @@
       </c>
       <c r="J172" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K172" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L172" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M172" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N172" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O172" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P172" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q172" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R172" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S172" s="12">
         <f>M172*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="173" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18269,11 +18269,11 @@
         <v>1</v>
       </c>
       <c r="F173" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G173" s="11">
         <f>1*F173*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H173" s="7">
         <v>13</v>
@@ -18284,40 +18284,40 @@
       </c>
       <c r="J173" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K173" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L173" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M173" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N173" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O173" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P173" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q173" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R173" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S173" s="12">
         <f>M173*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="174" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18337,11 +18337,11 @@
         <v>1</v>
       </c>
       <c r="F174" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G174" s="11">
         <f>1*F174*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H174" s="7">
         <v>13</v>
@@ -18352,40 +18352,40 @@
       </c>
       <c r="J174" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K174" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L174" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M174" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N174" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O174" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P174" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q174" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R174" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S174" s="12">
         <f>M174*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="175" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18405,11 +18405,11 @@
         <v>1</v>
       </c>
       <c r="F175" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G175" s="11">
         <f>1*F175*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H175" s="7">
         <v>13</v>
@@ -18420,40 +18420,40 @@
       </c>
       <c r="J175" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K175" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L175" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M175" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N175" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O175" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P175" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q175" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R175" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S175" s="12">
         <f>M175*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="176" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18473,11 +18473,11 @@
         <v>1</v>
       </c>
       <c r="F176" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G176" s="11">
         <f>1*F176*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H176" s="7">
         <v>13</v>
@@ -18488,40 +18488,40 @@
       </c>
       <c r="J176" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K176" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L176" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M176" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N176" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O176" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P176" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q176" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R176" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S176" s="12">
         <f>M176*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="177" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18541,11 +18541,11 @@
         <v>1</v>
       </c>
       <c r="F177" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G177" s="11">
         <f>1*F177*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H177" s="7">
         <v>13</v>
@@ -18556,40 +18556,40 @@
       </c>
       <c r="J177" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K177" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L177" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M177" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N177" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O177" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P177" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q177" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R177" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S177" s="12">
         <f>M177*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="178" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18609,11 +18609,11 @@
         <v>1</v>
       </c>
       <c r="F178" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G178" s="11">
         <f>1*F178*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H178" s="7">
         <v>13</v>
@@ -18624,40 +18624,40 @@
       </c>
       <c r="J178" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K178" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L178" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M178" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N178" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O178" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P178" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q178" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R178" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S178" s="12">
         <f>M178*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="179" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18677,11 +18677,11 @@
         <v>1</v>
       </c>
       <c r="F179" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G179" s="11">
         <f>1*F179*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H179" s="7">
         <v>13</v>
@@ -18692,40 +18692,40 @@
       </c>
       <c r="J179" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K179" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L179" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M179" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N179" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O179" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P179" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q179" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R179" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S179" s="12">
         <f>M179*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="180" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18745,11 +18745,11 @@
         <v>1</v>
       </c>
       <c r="F180" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G180" s="11">
         <f>1*F180*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H180" s="7">
         <v>13</v>
@@ -18760,40 +18760,40 @@
       </c>
       <c r="J180" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K180" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L180" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M180" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N180" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O180" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P180" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q180" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R180" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S180" s="12">
         <f>M180*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="181" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18813,11 +18813,11 @@
         <v>1</v>
       </c>
       <c r="F181" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G181" s="11">
         <f>1*F181*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H181" s="7">
         <v>13</v>
@@ -18828,40 +18828,40 @@
       </c>
       <c r="J181" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K181" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L181" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M181" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N181" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O181" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P181" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q181" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R181" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S181" s="12">
         <f>M181*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="182" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18881,11 +18881,11 @@
         <v>1</v>
       </c>
       <c r="F182" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G182" s="11">
         <f>1*F182*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H182" s="7">
         <v>13</v>
@@ -18896,40 +18896,40 @@
       </c>
       <c r="J182" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K182" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L182" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M182" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N182" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O182" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P182" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q182" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R182" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S182" s="12">
         <f>M182*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="183" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -18949,11 +18949,11 @@
         <v>1</v>
       </c>
       <c r="F183" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G183" s="11">
         <f>1*F183*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H183" s="7">
         <v>13</v>
@@ -18964,40 +18964,40 @@
       </c>
       <c r="J183" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K183" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L183" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M183" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N183" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O183" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P183" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q183" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R183" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S183" s="12">
         <f>M183*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="184" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19017,11 +19017,11 @@
         <v>1</v>
       </c>
       <c r="F184" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G184" s="11">
         <f>1*F184*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H184" s="7">
         <v>13</v>
@@ -19032,40 +19032,40 @@
       </c>
       <c r="J184" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K184" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L184" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M184" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N184" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O184" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P184" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q184" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R184" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S184" s="12">
         <f>M184*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="185" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19085,11 +19085,11 @@
         <v>1</v>
       </c>
       <c r="F185" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G185" s="11">
         <f>1*F185*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H185" s="7">
         <v>13</v>
@@ -19100,40 +19100,40 @@
       </c>
       <c r="J185" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K185" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L185" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M185" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N185" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O185" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P185" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q185" s="7">
         <f t="shared" si="13"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R185" s="7">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S185" s="12">
         <f>M185*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="186" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19153,55 +19153,55 @@
         <v>1</v>
       </c>
       <c r="F186" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G186" s="11">
         <f>1*F186*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H186" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I186" s="11">
         <f>H186*GiaDinh!$C$16</f>
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="J186" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K186" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L186" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M186" s="11">
-        <v>26.111000000000001</v>
+        <v>15</v>
       </c>
       <c r="N186" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(11.111/GiaDinh!$C$5-0.0005,0)</f>
-        <v>5</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O186" s="7">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P186" s="7">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q186" s="7">
         <f t="shared" si="13"/>
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="R186" s="7">
         <f t="shared" si="14"/>
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="S186" s="12">
         <f>M186*GiaDinh!$C$7</f>
-        <v>78.594110000000001</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="187" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19221,18 +19221,18 @@
         <v>1</v>
       </c>
       <c r="F187" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G187" s="11">
         <f>1*F187*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H187" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I187" s="11">
         <f>H187*GiaDinh!$C$16</f>
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="J187" s="7">
         <f t="shared" si="10"/>
@@ -19246,30 +19246,30 @@
         <v>ĐỦ</v>
       </c>
       <c r="M187" s="11">
-        <v>30</v>
+        <v>26.111000000000001</v>
       </c>
       <c r="N187" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(11.111/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>5</v>
       </c>
       <c r="O187" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P187" s="7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q187" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R187" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S187" s="12">
         <f>M187*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>78.594110000000001</v>
       </c>
     </row>
     <row r="188" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19289,11 +19289,11 @@
         <v>1</v>
       </c>
       <c r="F188" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G188" s="11">
         <f>1*F188*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H188" s="7">
         <v>12</v>
@@ -19304,40 +19304,40 @@
       </c>
       <c r="J188" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K188" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L188" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M188" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N188" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O188" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P188" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q188" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R188" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S188" s="12">
         <f>M188*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="189" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19357,11 +19357,11 @@
         <v>1</v>
       </c>
       <c r="F189" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G189" s="11">
         <f>1*F189*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H189" s="7">
         <v>12</v>
@@ -19372,40 +19372,40 @@
       </c>
       <c r="J189" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K189" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L189" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M189" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N189" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O189" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P189" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q189" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R189" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S189" s="12">
         <f>M189*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="190" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19425,11 +19425,11 @@
         <v>1</v>
       </c>
       <c r="F190" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G190" s="11">
         <f>1*F190*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H190" s="7">
         <v>12</v>
@@ -19440,40 +19440,40 @@
       </c>
       <c r="J190" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K190" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L190" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M190" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N190" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O190" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P190" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q190" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R190" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S190" s="12">
         <f>M190*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="191" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19493,11 +19493,11 @@
         <v>1</v>
       </c>
       <c r="F191" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G191" s="11">
         <f>1*F191*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H191" s="7">
         <v>12</v>
@@ -19508,40 +19508,40 @@
       </c>
       <c r="J191" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K191" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L191" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M191" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N191" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O191" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P191" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q191" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R191" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S191" s="12">
         <f>M191*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="192" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19561,11 +19561,11 @@
         <v>1</v>
       </c>
       <c r="F192" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G192" s="11">
         <f>1*F192*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H192" s="7">
         <v>12</v>
@@ -19576,40 +19576,40 @@
       </c>
       <c r="J192" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K192" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L192" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M192" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N192" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O192" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P192" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q192" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R192" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S192" s="12">
         <f>M192*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="193" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19629,11 +19629,11 @@
         <v>1</v>
       </c>
       <c r="F193" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G193" s="11">
         <f>1*F193*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H193" s="7">
         <v>12</v>
@@ -19644,40 +19644,40 @@
       </c>
       <c r="J193" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K193" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L193" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M193" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N193" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O193" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P193" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q193" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R193" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S193" s="12">
         <f>M193*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="194" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19697,11 +19697,11 @@
         <v>1</v>
       </c>
       <c r="F194" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G194" s="11">
         <f>1*F194*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H194" s="7">
         <v>12</v>
@@ -19712,40 +19712,40 @@
       </c>
       <c r="J194" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K194" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L194" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M194" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N194" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O194" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P194" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q194" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R194" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S194" s="12">
         <f>M194*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="195" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19765,11 +19765,11 @@
         <v>1</v>
       </c>
       <c r="F195" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G195" s="11">
         <f>1*F195*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H195" s="7">
         <v>12</v>
@@ -19780,40 +19780,40 @@
       </c>
       <c r="J195" s="7">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K195" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L195" s="7" t="str">
         <f t="shared" si="11"/>
         <v>ĐỦ</v>
       </c>
       <c r="M195" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N195" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O195" s="7">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P195" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q195" s="7">
         <f t="shared" si="13"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R195" s="7">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S195" s="12">
         <f>M195*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="196" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19833,11 +19833,11 @@
         <v>1</v>
       </c>
       <c r="F196" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G196" s="11">
         <f>1*F196*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H196" s="7">
         <v>12</v>
@@ -19848,40 +19848,40 @@
       </c>
       <c r="J196" s="7">
         <f t="shared" ref="J196:J259" si="15">MAX(1,ROUNDUP(G196/I196-0.0005,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K196" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L196" s="7" t="str">
         <f t="shared" ref="L196:L259" si="16">IF(K196&gt;=J196,"ĐỦ","THIẾU")</f>
         <v>ĐỦ</v>
       </c>
       <c r="M196" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N196" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O196" s="7">
         <f t="shared" ref="O196:O259" si="17">N196-K196</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P196" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q196" s="7">
         <f t="shared" ref="Q196:Q259" si="18">2*P196</f>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R196" s="7">
         <f t="shared" ref="R196:R259" si="19">P196</f>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S196" s="12">
         <f>M196*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="197" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19901,11 +19901,11 @@
         <v>1</v>
       </c>
       <c r="F197" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G197" s="11">
         <f>1*F197*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H197" s="7">
         <v>12</v>
@@ -19916,40 +19916,40 @@
       </c>
       <c r="J197" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K197" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L197" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M197" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N197" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O197" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P197" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q197" s="7">
         <f t="shared" si="18"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R197" s="7">
         <f t="shared" si="19"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S197" s="12">
         <f>M197*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="198" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -19969,7 +19969,7 @@
         <v>1</v>
       </c>
       <c r="F198" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G198" s="11">
         <f>0*F198*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -20037,7 +20037,7 @@
         <v>1</v>
       </c>
       <c r="F199" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G199" s="11">
         <f>0*F199*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -20105,7 +20105,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G200" s="11">
         <f>0*F200*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -20173,7 +20173,7 @@
         <v>1</v>
       </c>
       <c r="F201" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G201" s="11">
         <f>0*F201*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -20241,7 +20241,7 @@
         <v>1</v>
       </c>
       <c r="F202" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G202" s="11">
         <f>0*F202*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -20309,7 +20309,7 @@
         <v>1</v>
       </c>
       <c r="F203" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G203" s="11">
         <f>0*F203*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -20377,7 +20377,7 @@
         <v>1</v>
       </c>
       <c r="F204" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G204" s="11">
         <f>0*F204*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -20402,10 +20402,10 @@
         <v>ĐỦ</v>
       </c>
       <c r="M204" s="11">
-        <v>45</v>
+        <v>44.366999999999997</v>
       </c>
       <c r="N204" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.367/GiaDinh!$C$5-0.0005,0)</f>
         <v>9</v>
       </c>
       <c r="O204" s="7">
@@ -20425,7 +20425,7 @@
       </c>
       <c r="S204" s="12">
         <f>M204*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>133.54467</v>
       </c>
     </row>
     <row r="205" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -20445,7 +20445,7 @@
         <v>1</v>
       </c>
       <c r="F205" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G205" s="11">
         <f>0*F205*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -20513,11 +20513,11 @@
         <v>2</v>
       </c>
       <c r="F206" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G206" s="11">
         <f>2*F206*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H206" s="7">
         <v>13</v>
@@ -20528,40 +20528,40 @@
       </c>
       <c r="J206" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K206" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L206" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M206" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N206" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O206" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P206" s="7">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="Q206" s="7">
         <f t="shared" si="18"/>
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="R206" s="7">
         <f t="shared" si="19"/>
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="S206" s="12">
         <f>M206*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="207" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -20581,11 +20581,11 @@
         <v>2</v>
       </c>
       <c r="F207" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G207" s="11">
         <f>2*F207*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H207" s="7">
         <v>12</v>
@@ -20596,40 +20596,40 @@
       </c>
       <c r="J207" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K207" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L207" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M207" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N207" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O207" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P207" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q207" s="7">
         <f t="shared" si="18"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R207" s="7">
         <f t="shared" si="19"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S207" s="12">
         <f>M207*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="208" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -20649,11 +20649,11 @@
         <v>2</v>
       </c>
       <c r="F208" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G208" s="11">
         <f>2*F208*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H208" s="7">
         <v>14</v>
@@ -20664,40 +20664,40 @@
       </c>
       <c r="J208" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K208" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L208" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M208" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N208" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O208" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P208" s="7">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Q208" s="7">
         <f t="shared" si="18"/>
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="R208" s="7">
         <f t="shared" si="19"/>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="S208" s="12">
         <f>M208*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="209" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -20717,11 +20717,11 @@
         <v>2</v>
       </c>
       <c r="F209" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G209" s="11">
         <f>2*F209*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H209" s="7">
         <v>12</v>
@@ -20732,40 +20732,40 @@
       </c>
       <c r="J209" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K209" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L209" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M209" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N209" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O209" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P209" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q209" s="7">
         <f t="shared" si="18"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R209" s="7">
         <f t="shared" si="19"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S209" s="12">
         <f>M209*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="210" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -20785,11 +20785,11 @@
         <v>2</v>
       </c>
       <c r="F210" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G210" s="11">
         <f>2*F210*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H210" s="7">
         <v>12</v>
@@ -20800,40 +20800,40 @@
       </c>
       <c r="J210" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K210" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L210" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M210" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N210" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O210" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P210" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q210" s="7">
         <f t="shared" si="18"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R210" s="7">
         <f t="shared" si="19"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S210" s="12">
         <f>M210*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="211" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -20853,11 +20853,11 @@
         <v>2</v>
       </c>
       <c r="F211" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G211" s="11">
         <f>2*F211*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H211" s="7">
         <v>14</v>
@@ -20868,40 +20868,40 @@
       </c>
       <c r="J211" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K211" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L211" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M211" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N211" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O211" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P211" s="7">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Q211" s="7">
         <f t="shared" si="18"/>
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="R211" s="7">
         <f t="shared" si="19"/>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="S211" s="12">
         <f>M211*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="212" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -20921,11 +20921,11 @@
         <v>2</v>
       </c>
       <c r="F212" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G212" s="11">
         <f>2*F212*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H212" s="7">
         <v>12</v>
@@ -20936,40 +20936,40 @@
       </c>
       <c r="J212" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K212" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L212" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M212" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N212" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O212" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P212" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q212" s="7">
         <f t="shared" si="18"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R212" s="7">
         <f t="shared" si="19"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S212" s="12">
         <f>M212*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="213" spans="1:19" ht="31" x14ac:dyDescent="0.35">
@@ -20989,11 +20989,11 @@
         <v>4</v>
       </c>
       <c r="F213" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G213" s="11">
         <f>4*F213*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>409.584</v>
+        <v>319.87200000000001</v>
       </c>
       <c r="H213" s="7">
         <v>12</v>
@@ -21004,40 +21004,40 @@
       </c>
       <c r="J213" s="7">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K213" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L213" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M213" s="11">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N213" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>15</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>12</v>
       </c>
       <c r="O213" s="7">
         <f t="shared" si="17"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P213" s="7">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="Q213" s="7">
         <f t="shared" si="18"/>
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="R213" s="7">
         <f t="shared" si="19"/>
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="S213" s="12">
         <f>M213*GiaDinh!$C$7</f>
-        <v>225.74999999999997</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="214" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21057,11 +21057,11 @@
         <v>2</v>
       </c>
       <c r="F214" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G214" s="11">
         <f>2*F214*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H214" s="7">
         <v>10</v>
@@ -21125,11 +21125,11 @@
         <v>2</v>
       </c>
       <c r="F215" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G215" s="11">
         <f>2*F215*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H215" s="7">
         <v>12</v>
@@ -21140,40 +21140,40 @@
       </c>
       <c r="J215" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K215" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L215" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M215" s="11">
-        <v>44.058999999999997</v>
+        <v>29.373000000000001</v>
       </c>
       <c r="N215" s="7">
-        <f>ROUNDUP(14.686/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.686/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.686/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(14.686/GiaDinh!$C$5-0.0005,0)+ROUNDUP(14.686/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O215" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P215" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q215" s="7">
         <f t="shared" si="18"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R215" s="7">
         <f t="shared" si="19"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S215" s="12">
         <f>M215*GiaDinh!$C$7</f>
-        <v>132.61758999999998</v>
+        <v>88.412729999999996</v>
       </c>
     </row>
     <row r="216" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21193,11 +21193,11 @@
         <v>2</v>
       </c>
       <c r="F216" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G216" s="11">
         <f>2*F216*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H216" s="7">
         <v>13</v>
@@ -21208,40 +21208,40 @@
       </c>
       <c r="J216" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K216" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L216" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M216" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N216" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O216" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P216" s="7">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="Q216" s="7">
         <f t="shared" si="18"/>
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="R216" s="7">
         <f t="shared" si="19"/>
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="S216" s="12">
         <f>M216*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="217" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21261,11 +21261,11 @@
         <v>2</v>
       </c>
       <c r="F217" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G217" s="11">
         <f>2*F217*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H217" s="7">
         <v>9</v>
@@ -21276,40 +21276,40 @@
       </c>
       <c r="J217" s="7">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K217" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L217" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M217" s="11">
-        <v>47.773000000000003</v>
+        <v>36.848999999999997</v>
       </c>
       <c r="N217" s="7">
-        <f>ROUNDUP(10.924/GiaDinh!$C$5-0.0005,0)+ROUNDUP(10.924/GiaDinh!$C$5-0.0005,0)+ROUNDUP(10.924/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(10.924/GiaDinh!$C$5-0.0005,0)+ROUNDUP(10.924/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>7</v>
       </c>
       <c r="O217" s="7">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P217" s="7">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="Q217" s="7">
         <f t="shared" si="18"/>
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="R217" s="7">
         <f t="shared" si="19"/>
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S217" s="12">
         <f>M217*GiaDinh!$C$7</f>
-        <v>143.79673</v>
+        <v>110.91548999999998</v>
       </c>
     </row>
     <row r="218" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21329,11 +21329,11 @@
         <v>2</v>
       </c>
       <c r="F218" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G218" s="11">
         <f>2*F218*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H218" s="7">
         <v>12</v>
@@ -21344,40 +21344,40 @@
       </c>
       <c r="J218" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K218" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L218" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M218" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N218" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O218" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P218" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q218" s="7">
         <f t="shared" si="18"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R218" s="7">
         <f t="shared" si="19"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S218" s="12">
         <f>M218*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="219" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21397,11 +21397,11 @@
         <v>2</v>
       </c>
       <c r="F219" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G219" s="11">
         <f>2*F219*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H219" s="7">
         <v>12</v>
@@ -21412,40 +21412,40 @@
       </c>
       <c r="J219" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K219" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L219" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M219" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N219" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O219" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P219" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q219" s="7">
         <f t="shared" si="18"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R219" s="7">
         <f t="shared" si="19"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S219" s="12">
         <f>M219*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="220" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21465,11 +21465,11 @@
         <v>2</v>
       </c>
       <c r="F220" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G220" s="11">
         <f>2*F220*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>204.792</v>
+        <v>159.93600000000001</v>
       </c>
       <c r="H220" s="7">
         <v>12</v>
@@ -21480,40 +21480,40 @@
       </c>
       <c r="J220" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K220" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L220" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M220" s="11">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N220" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>9</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>6</v>
       </c>
       <c r="O220" s="7">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P220" s="7">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q220" s="7">
         <f t="shared" si="18"/>
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R220" s="7">
         <f t="shared" si="19"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S220" s="12">
         <f>M220*GiaDinh!$C$7</f>
-        <v>135.44999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="221" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21533,11 +21533,11 @@
         <v>1</v>
       </c>
       <c r="F221" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G221" s="11">
         <f>1*F221*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H221" s="7">
         <v>13</v>
@@ -21548,40 +21548,40 @@
       </c>
       <c r="J221" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K221" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L221" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M221" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N221" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O221" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P221" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q221" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R221" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S221" s="12">
         <f>M221*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="222" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21601,11 +21601,11 @@
         <v>1</v>
       </c>
       <c r="F222" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G222" s="11">
         <f>1*F222*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H222" s="7">
         <v>13</v>
@@ -21616,40 +21616,40 @@
       </c>
       <c r="J222" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K222" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L222" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M222" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N222" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O222" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P222" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q222" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R222" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S222" s="12">
         <f>M222*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="223" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21669,11 +21669,11 @@
         <v>1</v>
       </c>
       <c r="F223" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G223" s="11">
         <f>1*F223*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H223" s="7">
         <v>13</v>
@@ -21684,40 +21684,40 @@
       </c>
       <c r="J223" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K223" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L223" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M223" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N223" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O223" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P223" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q223" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R223" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S223" s="12">
         <f>M223*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="224" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21737,11 +21737,11 @@
         <v>1</v>
       </c>
       <c r="F224" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G224" s="11">
         <f>1*F224*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H224" s="7">
         <v>13</v>
@@ -21752,40 +21752,40 @@
       </c>
       <c r="J224" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K224" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L224" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M224" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N224" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O224" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P224" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q224" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R224" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S224" s="12">
         <f>M224*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="225" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21805,11 +21805,11 @@
         <v>1</v>
       </c>
       <c r="F225" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G225" s="11">
         <f>1*F225*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H225" s="7">
         <v>13</v>
@@ -21820,40 +21820,40 @@
       </c>
       <c r="J225" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K225" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L225" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M225" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N225" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O225" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P225" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q225" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R225" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S225" s="12">
         <f>M225*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="226" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21873,11 +21873,11 @@
         <v>1</v>
       </c>
       <c r="F226" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G226" s="11">
         <f>1*F226*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H226" s="7">
         <v>13</v>
@@ -21888,40 +21888,40 @@
       </c>
       <c r="J226" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K226" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L226" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M226" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N226" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O226" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P226" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q226" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R226" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S226" s="12">
         <f>M226*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="227" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -21941,11 +21941,11 @@
         <v>1</v>
       </c>
       <c r="F227" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G227" s="11">
         <f>1*F227*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H227" s="7">
         <v>13</v>
@@ -21956,40 +21956,40 @@
       </c>
       <c r="J227" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K227" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L227" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M227" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N227" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O227" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P227" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q227" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R227" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S227" s="12">
         <f>M227*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="228" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22009,11 +22009,11 @@
         <v>1</v>
       </c>
       <c r="F228" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G228" s="11">
         <f>1*F228*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H228" s="7">
         <v>13</v>
@@ -22024,40 +22024,40 @@
       </c>
       <c r="J228" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K228" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L228" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M228" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N228" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O228" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P228" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q228" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R228" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S228" s="12">
         <f>M228*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="229" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22077,11 +22077,11 @@
         <v>1</v>
       </c>
       <c r="F229" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G229" s="11">
         <f>1*F229*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H229" s="7">
         <v>13</v>
@@ -22092,40 +22092,40 @@
       </c>
       <c r="J229" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K229" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L229" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M229" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N229" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O229" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P229" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q229" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R229" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S229" s="12">
         <f>M229*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="230" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22145,11 +22145,11 @@
         <v>1</v>
       </c>
       <c r="F230" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G230" s="11">
         <f>1*F230*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H230" s="7">
         <v>13</v>
@@ -22160,40 +22160,40 @@
       </c>
       <c r="J230" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K230" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L230" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M230" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N230" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O230" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P230" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q230" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R230" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S230" s="12">
         <f>M230*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="231" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22213,11 +22213,11 @@
         <v>1</v>
       </c>
       <c r="F231" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G231" s="11">
         <f>1*F231*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H231" s="7">
         <v>13</v>
@@ -22228,40 +22228,40 @@
       </c>
       <c r="J231" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K231" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L231" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M231" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N231" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O231" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P231" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q231" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R231" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S231" s="12">
         <f>M231*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="232" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22281,11 +22281,11 @@
         <v>1</v>
       </c>
       <c r="F232" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G232" s="11">
         <f>1*F232*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H232" s="7">
         <v>13</v>
@@ -22296,40 +22296,40 @@
       </c>
       <c r="J232" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K232" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L232" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M232" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N232" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O232" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P232" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q232" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R232" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S232" s="12">
         <f>M232*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="233" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22349,11 +22349,11 @@
         <v>1</v>
       </c>
       <c r="F233" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G233" s="11">
         <f>1*F233*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H233" s="7">
         <v>13</v>
@@ -22364,40 +22364,40 @@
       </c>
       <c r="J233" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K233" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L233" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M233" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N233" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O233" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P233" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q233" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R233" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S233" s="12">
         <f>M233*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="234" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22417,11 +22417,11 @@
         <v>1</v>
       </c>
       <c r="F234" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G234" s="11">
         <f>1*F234*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H234" s="7">
         <v>13</v>
@@ -22432,40 +22432,40 @@
       </c>
       <c r="J234" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K234" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L234" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M234" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N234" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O234" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P234" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q234" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R234" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S234" s="12">
         <f>M234*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="235" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22485,11 +22485,11 @@
         <v>1</v>
       </c>
       <c r="F235" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G235" s="11">
         <f>1*F235*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H235" s="7">
         <v>13</v>
@@ -22500,40 +22500,40 @@
       </c>
       <c r="J235" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K235" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L235" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M235" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N235" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O235" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P235" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q235" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R235" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S235" s="12">
         <f>M235*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="236" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22553,11 +22553,11 @@
         <v>1</v>
       </c>
       <c r="F236" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G236" s="11">
         <f>1*F236*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H236" s="7">
         <v>13</v>
@@ -22568,40 +22568,40 @@
       </c>
       <c r="J236" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K236" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L236" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M236" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N236" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O236" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P236" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q236" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R236" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S236" s="12">
         <f>M236*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="237" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22621,11 +22621,11 @@
         <v>1</v>
       </c>
       <c r="F237" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G237" s="11">
         <f>1*F237*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H237" s="7">
         <v>13</v>
@@ -22636,40 +22636,40 @@
       </c>
       <c r="J237" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K237" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L237" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M237" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N237" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O237" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P237" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q237" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R237" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S237" s="12">
         <f>M237*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="238" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22689,11 +22689,11 @@
         <v>1</v>
       </c>
       <c r="F238" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G238" s="11">
         <f>1*F238*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H238" s="7">
         <v>13</v>
@@ -22704,40 +22704,40 @@
       </c>
       <c r="J238" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K238" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L238" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M238" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N238" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O238" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P238" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q238" s="7">
         <f t="shared" si="18"/>
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="R238" s="7">
         <f t="shared" si="19"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S238" s="12">
         <f>M238*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="239" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22757,11 +22757,11 @@
         <v>1</v>
       </c>
       <c r="F239" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G239" s="11">
         <f>1*F239*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H239" s="7">
         <v>12</v>
@@ -22772,40 +22772,40 @@
       </c>
       <c r="J239" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K239" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L239" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M239" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N239" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O239" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P239" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q239" s="7">
         <f t="shared" si="18"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R239" s="7">
         <f t="shared" si="19"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S239" s="12">
         <f>M239*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="240" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22825,11 +22825,11 @@
         <v>1</v>
       </c>
       <c r="F240" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G240" s="11">
         <f>1*F240*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H240" s="7">
         <v>12</v>
@@ -22840,40 +22840,40 @@
       </c>
       <c r="J240" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K240" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L240" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M240" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N240" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O240" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P240" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q240" s="7">
         <f t="shared" si="18"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R240" s="7">
         <f t="shared" si="19"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S240" s="12">
         <f>M240*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="241" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -22893,7 +22893,7 @@
         <v>1</v>
       </c>
       <c r="F241" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G241" s="11">
         <f>0*F241*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -22961,7 +22961,7 @@
         <v>1</v>
       </c>
       <c r="F242" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G242" s="11">
         <f>0*F242*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -23029,7 +23029,7 @@
         <v>1</v>
       </c>
       <c r="F243" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G243" s="11">
         <f>0*F243*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -23097,7 +23097,7 @@
         <v>1</v>
       </c>
       <c r="F244" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G244" s="11">
         <f>0*F244*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -23165,7 +23165,7 @@
         <v>1</v>
       </c>
       <c r="F245" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G245" s="11">
         <f>0*F245*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -23233,7 +23233,7 @@
         <v>1</v>
       </c>
       <c r="F246" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G246" s="11">
         <f>0*F246*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -23301,7 +23301,7 @@
         <v>1</v>
       </c>
       <c r="F247" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G247" s="11">
         <f>0*F247*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -23369,7 +23369,7 @@
         <v>1</v>
       </c>
       <c r="F248" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G248" s="11">
         <f>0*F248*GiaDinh!$C$18*GiaDinh!$C$17+154.8*GiaDinh!$C$17</f>
@@ -23437,11 +23437,11 @@
         <v>1</v>
       </c>
       <c r="F249" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G249" s="11">
         <f>1*F249*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H249" s="7">
         <v>12</v>
@@ -23452,40 +23452,40 @@
       </c>
       <c r="J249" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K249" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L249" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M249" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N249" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O249" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P249" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q249" s="7">
         <f t="shared" si="18"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R249" s="7">
         <f t="shared" si="19"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S249" s="12">
         <f>M249*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="250" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -23505,11 +23505,11 @@
         <v>1</v>
       </c>
       <c r="F250" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G250" s="11">
         <f>1*F250*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H250" s="7">
         <v>12</v>
@@ -23520,40 +23520,40 @@
       </c>
       <c r="J250" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K250" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L250" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M250" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N250" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O250" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P250" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q250" s="7">
         <f t="shared" si="18"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R250" s="7">
         <f t="shared" si="19"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S250" s="12">
         <f>M250*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="251" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -23573,11 +23573,11 @@
         <v>1</v>
       </c>
       <c r="F251" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G251" s="11">
         <f>1*F251*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H251" s="7">
         <v>12</v>
@@ -23588,40 +23588,40 @@
       </c>
       <c r="J251" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K251" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L251" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M251" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N251" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O251" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P251" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q251" s="7">
         <f t="shared" si="18"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R251" s="7">
         <f t="shared" si="19"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S251" s="12">
         <f>M251*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="252" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -23641,11 +23641,11 @@
         <v>1</v>
       </c>
       <c r="F252" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G252" s="11">
         <f>1*F252*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H252" s="7">
         <v>12</v>
@@ -23656,40 +23656,40 @@
       </c>
       <c r="J252" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K252" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L252" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M252" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N252" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O252" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P252" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q252" s="7">
         <f t="shared" si="18"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R252" s="7">
         <f t="shared" si="19"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S252" s="12">
         <f>M252*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="253" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -23709,11 +23709,11 @@
         <v>1</v>
       </c>
       <c r="F253" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G253" s="11">
         <f>1*F253*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H253" s="7">
         <v>12</v>
@@ -23724,40 +23724,40 @@
       </c>
       <c r="J253" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K253" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L253" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M253" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N253" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O253" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P253" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q253" s="7">
         <f t="shared" si="18"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R253" s="7">
         <f t="shared" si="19"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S253" s="12">
         <f>M253*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="254" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -23777,11 +23777,11 @@
         <v>1</v>
       </c>
       <c r="F254" s="7">
-        <v>121.9</v>
+        <v>95.2</v>
       </c>
       <c r="G254" s="11">
         <f>1*F254*GiaDinh!$C$18*GiaDinh!$C$17</f>
-        <v>102.396</v>
+        <v>79.968000000000004</v>
       </c>
       <c r="H254" s="7">
         <v>12</v>
@@ -23792,40 +23792,40 @@
       </c>
       <c r="J254" s="7">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K254" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L254" s="7" t="str">
         <f t="shared" si="16"/>
         <v>ĐỦ</v>
       </c>
       <c r="M254" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N254" s="7">
-        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)+ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
-        <v>6</v>
+        <f>ROUNDUP(15/GiaDinh!$C$5-0.0005,0)</f>
+        <v>3</v>
       </c>
       <c r="O254" s="7">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P254" s="7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q254" s="7">
         <f t="shared" si="18"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R254" s="7">
         <f t="shared" si="19"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S254" s="12">
         <f>M254*GiaDinh!$C$7</f>
-        <v>90.3</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="255" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
@@ -45121,7 +45121,7 @@
         <v>0.39</v>
       </c>
       <c r="J5" s="7">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K5" s="8">
         <v>22397</v>
@@ -45159,7 +45159,7 @@
         <v>0.76</v>
       </c>
       <c r="J6" s="7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K6" s="8">
         <v>3966</v>
@@ -45305,7 +45305,7 @@
       <c r="I10" s="16"/>
       <c r="J10" s="17">
         <f>SUM(J4:J9)</f>
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="K10" s="17">
         <f>SUM(K4:K9)</f>
